--- a/grupos/3ARHV - Estadisticos 20211.xlsx
+++ b/grupos/3ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="356" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -185,24 +185,24 @@
     <t>Por_Blancos</t>
   </si>
   <si>
+    <t>Hernández Mendoza Delfina</t>
+  </si>
+  <si>
+    <t>Mendoza Velazquez Laura Elena</t>
+  </si>
+  <si>
+    <t>González Nuñez Veronica</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Hernández Mendoza Delfina</t>
+    <t>Muñoz Rivadeneyra Salvador</t>
   </si>
   <si>
     <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
-    <t>González Nuñez Veronica</t>
-  </si>
-  <si>
-    <t>Mendoza Velazquez Laura Elena</t>
-  </si>
-  <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -218,253 +218,253 @@
     <t>FLORES</t>
   </si>
   <si>
+    <t>HERNANDEZ</t>
+  </si>
+  <si>
+    <t>MARROQUIN</t>
+  </si>
+  <si>
+    <t>MARCIAL</t>
+  </si>
+  <si>
+    <t>OSORIO</t>
+  </si>
+  <si>
+    <t>DE LA ROSA</t>
+  </si>
+  <si>
+    <t>ROSAS</t>
+  </si>
+  <si>
+    <t>SANCHEZ</t>
+  </si>
+  <si>
+    <t>TORRES</t>
+  </si>
+  <si>
+    <t>CERVANTES</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
+    <t>HERRERA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>MACHORRO</t>
+  </si>
+  <si>
+    <t>CASTRO</t>
+  </si>
+  <si>
+    <t>SALAZAR</t>
+  </si>
+  <si>
+    <t>RAMON</t>
+  </si>
+  <si>
+    <t>PEREZ</t>
+  </si>
+  <si>
+    <t>JAVIER</t>
+  </si>
+  <si>
+    <t>ESMERALDA</t>
+  </si>
+  <si>
+    <t>IVAN DE JESUS</t>
+  </si>
+  <si>
+    <t>KARLA</t>
+  </si>
+  <si>
+    <t>ALONDRA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MEILYN ADABEL</t>
+  </si>
+  <si>
+    <t>CONSTANZA XIMENA</t>
+  </si>
+  <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>GARCIA</t>
   </si>
   <si>
-    <t>HERNANDEZ</t>
-  </si>
-  <si>
     <t>JIMENEZ</t>
   </si>
   <si>
-    <t>MARROQUIN</t>
-  </si>
-  <si>
-    <t>MARCIAL</t>
-  </si>
-  <si>
-    <t>OSORIO</t>
-  </si>
-  <si>
-    <t>DE LA ROSA</t>
-  </si>
-  <si>
-    <t>ROSAS</t>
-  </si>
-  <si>
-    <t>SANCHEZ</t>
-  </si>
-  <si>
-    <t>TORRES</t>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
+    <t>TIBURCIO</t>
   </si>
   <si>
     <t>TRUJILLO</t>
   </si>
   <si>
-    <t>CERVANTES</t>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
   </si>
   <si>
     <t>JUAREZ</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
   </si>
   <si>
     <t>APARICIO</t>
   </si>
   <si>
-    <t>HERRERA</t>
-  </si>
-  <si>
-    <t>MORALES</t>
-  </si>
-  <si>
-    <t>MACHORRO</t>
-  </si>
-  <si>
-    <t>CASTRO</t>
-  </si>
-  <si>
-    <t>SALAZAR</t>
-  </si>
-  <si>
-    <t>RAMON</t>
-  </si>
-  <si>
-    <t>PEREZ</t>
-  </si>
-  <si>
-    <t>JAVIER</t>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
+  </si>
+  <si>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
+  </si>
+  <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
   </si>
   <si>
     <t>EMELIN JIROMI</t>
   </si>
   <si>
-    <t>ESMERALDA</t>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
   </si>
   <si>
     <t>YAZMIN</t>
   </si>
   <si>
-    <t>IVAN DE JESUS</t>
-  </si>
-  <si>
-    <t>KARLA</t>
-  </si>
-  <si>
-    <t>ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIA FERNANDA</t>
-  </si>
-  <si>
-    <t>MEILYN ADABEL</t>
-  </si>
-  <si>
-    <t>CONSTANZA XIMENA</t>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
+    <t>XIMENA MICHELL</t>
+  </si>
+  <si>
+    <t>DIANA VIANNEY</t>
   </si>
   <si>
     <t>KIMBERLY</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>VELAZQEZ</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
   </si>
   <si>
     <t>PAULINA</t>
@@ -971,22 +971,22 @@
         <v>9</v>
       </c>
       <c r="H4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K4">
         <v>-1</v>
       </c>
       <c r="L4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="N4">
         <v>-1</v>
@@ -1007,19 +1007,19 @@
         <v>-1</v>
       </c>
       <c r="T4">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U4">
         <v>10</v>
       </c>
       <c r="V4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W4">
         <v>8</v>
       </c>
       <c r="X4">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y4">
         <v>9</v>
@@ -1048,22 +1048,22 @@
         <v>10</v>
       </c>
       <c r="H5">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K5">
         <v>-1</v>
       </c>
       <c r="L5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N5">
         <v>-1</v>
@@ -1084,19 +1084,19 @@
         <v>-1</v>
       </c>
       <c r="T5">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U5">
         <v>10</v>
       </c>
       <c r="V5">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y5">
         <v>10</v>
@@ -1125,22 +1125,22 @@
         <v>9</v>
       </c>
       <c r="H6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K6">
         <v>-1</v>
       </c>
       <c r="L6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N6">
         <v>-1</v>
@@ -1161,7 +1161,7 @@
         <v>-1</v>
       </c>
       <c r="T6">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U6">
         <v>10</v>
@@ -1176,7 +1176,7 @@
         <v>10</v>
       </c>
       <c r="Y6">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="7" spans="1:25">
@@ -1202,10 +1202,10 @@
         <v>8</v>
       </c>
       <c r="H7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I7">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J7">
         <v>-1</v>
@@ -1214,10 +1214,10 @@
         <v>-1</v>
       </c>
       <c r="L7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M7">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N7">
         <v>-1</v>
@@ -1238,7 +1238,7 @@
         <v>-1</v>
       </c>
       <c r="T7">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U7">
         <v>10</v>
@@ -1253,7 +1253,7 @@
         <v>7</v>
       </c>
       <c r="Y7">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1279,22 +1279,22 @@
         <v>8</v>
       </c>
       <c r="H8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K8">
         <v>-1</v>
       </c>
       <c r="L8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N8">
         <v>-1</v>
@@ -1315,10 +1315,10 @@
         <v>-1</v>
       </c>
       <c r="T8">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U8">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V8">
         <v>9</v>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1356,19 +1356,19 @@
         <v>-1</v>
       </c>
       <c r="H9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I9">
         <v>-1</v>
       </c>
       <c r="J9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K9">
         <v>-1</v>
       </c>
       <c r="L9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M9">
         <v>-1</v>
@@ -1392,13 +1392,13 @@
         <v>-1</v>
       </c>
       <c r="T9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U9">
         <v>-1</v>
       </c>
       <c r="V9">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W9">
         <v>5</v>
@@ -1421,7 +1421,7 @@
         <v>-1</v>
       </c>
       <c r="D10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="E10">
         <v>5</v>
@@ -1433,19 +1433,19 @@
         <v>-1</v>
       </c>
       <c r="H10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I10">
         <v>-1</v>
       </c>
       <c r="J10">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K10">
         <v>-1</v>
       </c>
       <c r="L10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M10">
         <v>-1</v>
@@ -1469,13 +1469,13 @@
         <v>-1</v>
       </c>
       <c r="T10">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U10">
         <v>-1</v>
       </c>
       <c r="V10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="W10">
         <v>5</v>
@@ -1495,7 +1495,7 @@
         <v>8</v>
       </c>
       <c r="C11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D11">
         <v>7</v>
@@ -1510,22 +1510,22 @@
         <v>9</v>
       </c>
       <c r="H11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K11">
         <v>-1</v>
       </c>
       <c r="L11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N11">
         <v>-1</v>
@@ -1546,22 +1546,22 @@
         <v>-1</v>
       </c>
       <c r="T11">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U11">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W11">
         <v>9</v>
       </c>
       <c r="X11">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y11">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1587,19 +1587,19 @@
         <v>9</v>
       </c>
       <c r="H12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I12">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K12">
         <v>-1</v>
       </c>
       <c r="L12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M12">
         <v>-1</v>
@@ -1623,13 +1623,13 @@
         <v>-1</v>
       </c>
       <c r="T12">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U12">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W12">
         <v>8</v>
@@ -1664,22 +1664,22 @@
         <v>7</v>
       </c>
       <c r="H13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I13">
         <v>-1</v>
       </c>
       <c r="J13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K13">
         <v>-1</v>
       </c>
       <c r="L13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N13">
         <v>-1</v>
@@ -1700,7 +1700,7 @@
         <v>-1</v>
       </c>
       <c r="T13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U13">
         <v>10</v>
@@ -1715,7 +1715,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1726,7 +1726,7 @@
         <v>5</v>
       </c>
       <c r="C14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D14">
         <v>9</v>
@@ -1741,7 +1741,7 @@
         <v>-1</v>
       </c>
       <c r="H14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I14">
         <v>-1</v>
@@ -1753,7 +1753,7 @@
         <v>-1</v>
       </c>
       <c r="L14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M14">
         <v>-1</v>
@@ -1777,10 +1777,10 @@
         <v>-1</v>
       </c>
       <c r="T14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U14">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V14">
         <v>9</v>
@@ -1818,22 +1818,22 @@
         <v>7</v>
       </c>
       <c r="H15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="I15">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K15">
         <v>-1</v>
       </c>
       <c r="L15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N15">
         <v>-1</v>
@@ -1895,22 +1895,22 @@
         <v>10</v>
       </c>
       <c r="H16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I16">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J16">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K16">
         <v>-1</v>
       </c>
       <c r="L16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N16">
         <v>-1</v>
@@ -1934,10 +1934,10 @@
         <v>10</v>
       </c>
       <c r="U16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V16">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W16">
         <v>8</v>
@@ -1946,7 +1946,7 @@
         <v>9</v>
       </c>
       <c r="Y16">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1957,7 +1957,7 @@
         <v>7</v>
       </c>
       <c r="C17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D17">
         <v>10</v>
@@ -1972,22 +1972,22 @@
         <v>9</v>
       </c>
       <c r="H17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K17">
         <v>-1</v>
       </c>
       <c r="L17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N17">
         <v>-1</v>
@@ -2008,10 +2008,10 @@
         <v>-1</v>
       </c>
       <c r="T17">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="U17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V17">
         <v>10</v>
@@ -2020,10 +2020,10 @@
         <v>8</v>
       </c>
       <c r="X17">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y17">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2049,22 +2049,22 @@
         <v>8</v>
       </c>
       <c r="H18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K18">
         <v>-1</v>
       </c>
       <c r="L18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M18">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N18">
         <v>-1</v>
@@ -2100,7 +2100,7 @@
         <v>9</v>
       </c>
       <c r="Y18">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="19" spans="1:25">
@@ -2126,22 +2126,22 @@
         <v>6</v>
       </c>
       <c r="H19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I19">
         <v>-1</v>
       </c>
       <c r="J19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K19">
         <v>-1</v>
       </c>
       <c r="L19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N19">
         <v>-1</v>
@@ -2162,7 +2162,7 @@
         <v>-1</v>
       </c>
       <c r="T19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U19">
         <v>10</v>
@@ -2203,7 +2203,7 @@
         <v>8</v>
       </c>
       <c r="H20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I20">
         <v>-1</v>
@@ -2215,7 +2215,7 @@
         <v>-1</v>
       </c>
       <c r="L20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="M20">
         <v>-1</v>
@@ -2239,7 +2239,7 @@
         <v>-1</v>
       </c>
       <c r="T20">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U20">
         <v>10</v>
@@ -2251,7 +2251,7 @@
         <v>9</v>
       </c>
       <c r="X20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y20">
         <v>8</v>
@@ -2280,19 +2280,19 @@
         <v>-1</v>
       </c>
       <c r="H21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I21">
         <v>-1</v>
       </c>
       <c r="J21">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K21">
         <v>-1</v>
       </c>
       <c r="L21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M21">
         <v>-1</v>
@@ -2316,7 +2316,7 @@
         <v>-1</v>
       </c>
       <c r="T21">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U21">
         <v>-1</v>
@@ -2328,7 +2328,7 @@
         <v>9</v>
       </c>
       <c r="X21">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y21">
         <v>-1</v>
@@ -2342,7 +2342,7 @@
         <v>5</v>
       </c>
       <c r="C22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D22">
         <v>8</v>
@@ -2357,7 +2357,7 @@
         <v>-1</v>
       </c>
       <c r="H22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I22">
         <v>-1</v>
@@ -2369,7 +2369,7 @@
         <v>-1</v>
       </c>
       <c r="L22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M22">
         <v>-1</v>
@@ -2396,7 +2396,7 @@
         <v>5</v>
       </c>
       <c r="U22">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V22">
         <v>8</v>
@@ -2434,7 +2434,7 @@
         <v>8</v>
       </c>
       <c r="H23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I23">
         <v>-1</v>
@@ -2446,7 +2446,7 @@
         <v>-1</v>
       </c>
       <c r="L23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M23">
         <v>-1</v>
@@ -2470,7 +2470,7 @@
         <v>-1</v>
       </c>
       <c r="T23">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U23">
         <v>10</v>
@@ -2511,22 +2511,22 @@
         <v>8</v>
       </c>
       <c r="H24">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I24">
         <v>-1</v>
       </c>
       <c r="J24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K24">
         <v>-1</v>
       </c>
       <c r="L24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M24">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N24">
         <v>-1</v>
@@ -2547,7 +2547,7 @@
         <v>-1</v>
       </c>
       <c r="T24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U24">
         <v>10</v>
@@ -2559,7 +2559,7 @@
         <v>10</v>
       </c>
       <c r="X24">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2588,22 +2588,22 @@
         <v>8</v>
       </c>
       <c r="H25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J25">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K25">
         <v>-1</v>
       </c>
       <c r="L25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N25">
         <v>-1</v>
@@ -2624,7 +2624,7 @@
         <v>-1</v>
       </c>
       <c r="T25">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U25">
         <v>10</v>
@@ -2636,10 +2636,10 @@
         <v>9</v>
       </c>
       <c r="X25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y25">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="26" spans="1:25">
@@ -2665,22 +2665,22 @@
         <v>6</v>
       </c>
       <c r="H26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I26">
         <v>-1</v>
       </c>
       <c r="J26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K26">
         <v>-1</v>
       </c>
       <c r="L26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N26">
         <v>-1</v>
@@ -2701,13 +2701,13 @@
         <v>-1</v>
       </c>
       <c r="T26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U26">
         <v>10</v>
       </c>
       <c r="V26">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2716,7 +2716,7 @@
         <v>6</v>
       </c>
       <c r="Y26">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="27" spans="1:25">
@@ -2742,22 +2742,22 @@
         <v>9</v>
       </c>
       <c r="H27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K27">
         <v>-1</v>
       </c>
       <c r="L27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N27">
         <v>-1</v>
@@ -2784,16 +2784,16 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W27">
         <v>10</v>
       </c>
       <c r="X27">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="Y27">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2819,7 +2819,7 @@
         <v>-1</v>
       </c>
       <c r="H28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I28">
         <v>-1</v>
@@ -2831,7 +2831,7 @@
         <v>-1</v>
       </c>
       <c r="L28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="M28">
         <v>-1</v>
@@ -2867,7 +2867,7 @@
         <v>5</v>
       </c>
       <c r="X28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="Y28">
         <v>-1</v>
@@ -2896,22 +2896,22 @@
         <v>6</v>
       </c>
       <c r="H29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K29">
         <v>-1</v>
       </c>
       <c r="L29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N29">
         <v>-1</v>
@@ -2932,10 +2932,10 @@
         <v>-1</v>
       </c>
       <c r="T29">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U29">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V29">
         <v>9</v>
@@ -2944,10 +2944,10 @@
         <v>8</v>
       </c>
       <c r="X29">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="Y29">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="30" spans="1:25">
@@ -2973,22 +2973,22 @@
         <v>10</v>
       </c>
       <c r="H30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K30">
         <v>-1</v>
       </c>
       <c r="L30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N30">
         <v>-1</v>
@@ -3009,7 +3009,7 @@
         <v>-1</v>
       </c>
       <c r="T30">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U30">
         <v>10</v>
@@ -3050,22 +3050,22 @@
         <v>10</v>
       </c>
       <c r="H31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="K31">
         <v>-1</v>
       </c>
       <c r="L31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="M31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N31">
         <v>-1</v>
@@ -3086,13 +3086,13 @@
         <v>-1</v>
       </c>
       <c r="T31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U31">
         <v>10</v>
       </c>
       <c r="V31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="W31">
         <v>9</v>
@@ -3127,19 +3127,19 @@
         <v>-1</v>
       </c>
       <c r="H32">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J32">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K32">
         <v>-1</v>
       </c>
       <c r="L32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M32">
         <v>-1</v>
@@ -3163,13 +3163,13 @@
         <v>-1</v>
       </c>
       <c r="T32">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="U32">
         <v>10</v>
       </c>
       <c r="V32">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W32">
         <v>5</v>
@@ -3204,22 +3204,22 @@
         <v>10</v>
       </c>
       <c r="H33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="I33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="K33">
         <v>-1</v>
       </c>
       <c r="L33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="M33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="N33">
         <v>-1</v>
@@ -3240,7 +3240,7 @@
         <v>-1</v>
       </c>
       <c r="T33">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="U33">
         <v>10</v>
@@ -3252,7 +3252,7 @@
         <v>9</v>
       </c>
       <c r="X33">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="Y33">
         <v>10</v>
@@ -3281,7 +3281,7 @@
         <v>-1</v>
       </c>
       <c r="H34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="I34">
         <v>-1</v>
@@ -3293,7 +3293,7 @@
         <v>-1</v>
       </c>
       <c r="L34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M34">
         <v>-1</v>
@@ -3317,7 +3317,7 @@
         <v>-1</v>
       </c>
       <c r="T34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="U34">
         <v>-1</v>
@@ -3358,22 +3358,22 @@
         <v>10</v>
       </c>
       <c r="H35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K35">
         <v>-1</v>
       </c>
       <c r="L35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N35">
         <v>-1</v>
@@ -3394,7 +3394,7 @@
         <v>-1</v>
       </c>
       <c r="T35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="U35">
         <v>10</v>
@@ -3420,7 +3420,7 @@
         <v>6</v>
       </c>
       <c r="C36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D36">
         <v>9</v>
@@ -3435,10 +3435,10 @@
         <v>-1</v>
       </c>
       <c r="H36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="I36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J36">
         <v>-1</v>
@@ -3447,7 +3447,7 @@
         <v>-1</v>
       </c>
       <c r="L36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="M36">
         <v>-1</v>
@@ -3471,10 +3471,10 @@
         <v>-1</v>
       </c>
       <c r="T36">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="U36">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="V36">
         <v>9</v>
@@ -3512,22 +3512,22 @@
         <v>8</v>
       </c>
       <c r="H37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="I37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="J37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K37">
         <v>-1</v>
       </c>
       <c r="L37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="M37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="N37">
         <v>-1</v>
@@ -3563,7 +3563,7 @@
         <v>10</v>
       </c>
       <c r="Y37">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -3619,7 +3619,7 @@
     </row>
     <row r="2" spans="1:10">
       <c r="A2" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="B2" t="s">
         <v>55</v>
@@ -3628,30 +3628,30 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E2">
         <v>0</v>
       </c>
       <c r="F2">
-        <v>71.43000000000001</v>
+        <v>74.29000000000001</v>
       </c>
       <c r="G2">
         <v>0</v>
       </c>
       <c r="H2">
-        <v>10</v>
+        <v>8.9</v>
       </c>
       <c r="I2">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="J2">
-        <v>28.57</v>
+        <v>25.71</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3660,30 +3660,30 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E3">
+        <v>8</v>
+      </c>
+      <c r="F3">
+        <v>77.14</v>
+      </c>
+      <c r="G3">
+        <v>22.86</v>
+      </c>
+      <c r="H3">
+        <v>7.7</v>
+      </c>
+      <c r="I3">
         <v>0</v>
       </c>
-      <c r="F3">
-        <v>74.29000000000001</v>
-      </c>
-      <c r="G3">
+      <c r="J3">
         <v>0</v>
-      </c>
-      <c r="H3">
-        <v>8.5</v>
-      </c>
-      <c r="I3">
-        <v>9</v>
-      </c>
-      <c r="J3">
-        <v>25.71</v>
       </c>
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>5</v>
+        <v>8</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3692,19 +3692,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="F4">
-        <v>80</v>
+        <v>82.86</v>
       </c>
       <c r="G4">
-        <v>20</v>
+        <v>17.14</v>
       </c>
       <c r="H4">
-        <v>7.2</v>
+        <v>8</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3724,30 +3724,30 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E5">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F5">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G5">
-        <v>17.14</v>
+        <v>0</v>
       </c>
       <c r="H5">
-        <v>8</v>
+        <v>9.9</v>
       </c>
       <c r="I5">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="J5">
-        <v>0</v>
+        <v>11.43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3756,30 +3756,30 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>29</v>
+        <v>32</v>
       </c>
       <c r="E6">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F6">
-        <v>82.86</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="G6">
-        <v>17.14</v>
+        <v>5.71</v>
       </c>
       <c r="H6">
-        <v>7.5</v>
+        <v>8.5</v>
       </c>
       <c r="I6">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J6">
-        <v>0</v>
+        <v>2.86</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -3788,25 +3788,25 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F7">
-        <v>88.56999999999999</v>
+        <v>91.43000000000001</v>
       </c>
       <c r="G7">
-        <v>5.71</v>
+        <v>8.57</v>
       </c>
       <c r="H7">
-        <v>8.300000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J7">
-        <v>5.71</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -3816,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F22"/>
+  <dimension ref="A1:F15"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3851,16 +3851,16 @@
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E2" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:6">
@@ -3871,33 +3871,33 @@
         <v>65</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="E3" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="4" spans="1:6">
       <c r="A4">
-        <v>20330051920122</v>
+        <v>20330051920126</v>
       </c>
       <c r="B4" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>84</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F4" t="s">
         <v>55</v>
@@ -3905,19 +3905,19 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5">
-        <v>20330051920123</v>
+        <v>20330051920135</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C5" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E5" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F5" t="s">
         <v>55</v>
@@ -3925,59 +3925,59 @@
     </row>
     <row r="6" spans="1:6">
       <c r="A6">
-        <v>20330051920126</v>
+        <v>20330051920136</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C6" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D6" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E6" t="s">
         <v>10</v>
       </c>
       <c r="F6" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="7" spans="1:6">
       <c r="A7">
-        <v>20330051920126</v>
+        <v>20330051920136</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C7" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D7" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E7" t="s">
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="8" spans="1:6">
       <c r="A8">
-        <v>20330051920129</v>
+        <v>20330051920141</v>
       </c>
       <c r="B8" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="E8" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F8" t="s">
         <v>55</v>
@@ -3985,278 +3985,141 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9">
-        <v>20330051920135</v>
+        <v>20330051920144</v>
       </c>
       <c r="B9" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D9" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E9" t="s">
         <v>10</v>
       </c>
       <c r="F9" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="10" spans="1:6">
       <c r="A10">
-        <v>20330051920135</v>
+        <v>20330051920144</v>
       </c>
       <c r="B10" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C10" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E10" t="s">
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="11" spans="1:6">
       <c r="A11">
-        <v>20330051920136</v>
+        <v>20330051920387</v>
       </c>
       <c r="B11" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C11" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D11" t="s">
-        <v>92</v>
+        <v>88</v>
       </c>
       <c r="E11" t="s">
         <v>10</v>
       </c>
       <c r="F11" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="12" spans="1:6">
       <c r="A12">
-        <v>20330051920136</v>
+        <v>20330051920148</v>
       </c>
       <c r="B12" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C12" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="D12" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F12" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920141</v>
+        <v>20330051920148</v>
       </c>
       <c r="B13" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C13" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="D13" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="E13" t="s">
         <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920144</v>
+        <v>20330051920148</v>
       </c>
       <c r="B14" t="s">
         <v>72</v>
       </c>
       <c r="C14" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="D14" t="s">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="E14" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F14" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
     </row>
     <row r="15" spans="1:6">
       <c r="A15">
-        <v>20330051920144</v>
+        <v>20330051920151</v>
       </c>
       <c r="B15" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C15" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="D15" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="E15" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F15" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6">
-      <c r="A16">
-        <v>20330051920387</v>
-      </c>
-      <c r="B16" t="s">
-        <v>73</v>
-      </c>
-      <c r="C16" t="s">
-        <v>85</v>
-      </c>
-      <c r="D16" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" t="s">
-        <v>10</v>
-      </c>
-      <c r="F16" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6">
-      <c r="A17">
-        <v>20330051920148</v>
-      </c>
-      <c r="B17" t="s">
-        <v>74</v>
-      </c>
-      <c r="C17" t="s">
-        <v>86</v>
-      </c>
-      <c r="D17" t="s">
-        <v>96</v>
-      </c>
-      <c r="E17" t="s">
-        <v>7</v>
-      </c>
-      <c r="F17" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6">
-      <c r="A18">
-        <v>20330051920148</v>
-      </c>
-      <c r="B18" t="s">
-        <v>74</v>
-      </c>
-      <c r="C18" t="s">
-        <v>86</v>
-      </c>
-      <c r="D18" t="s">
-        <v>96</v>
-      </c>
-      <c r="E18" t="s">
-        <v>10</v>
-      </c>
-      <c r="F18" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6">
-      <c r="A19">
-        <v>20330051920148</v>
-      </c>
-      <c r="B19" t="s">
-        <v>74</v>
-      </c>
-      <c r="C19" t="s">
-        <v>86</v>
-      </c>
-      <c r="D19" t="s">
-        <v>96</v>
-      </c>
-      <c r="E19" t="s">
-        <v>6</v>
-      </c>
-      <c r="F19" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6">
-      <c r="A20">
-        <v>20330051920151</v>
-      </c>
-      <c r="B20" t="s">
-        <v>75</v>
-      </c>
-      <c r="C20" t="s">
-        <v>87</v>
-      </c>
-      <c r="D20" t="s">
-        <v>97</v>
-      </c>
-      <c r="E20" t="s">
-        <v>10</v>
-      </c>
-      <c r="F20" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6">
-      <c r="A21">
-        <v>20330051920151</v>
-      </c>
-      <c r="B21" t="s">
-        <v>75</v>
-      </c>
-      <c r="C21" t="s">
-        <v>87</v>
-      </c>
-      <c r="D21" t="s">
-        <v>97</v>
-      </c>
-      <c r="E21" t="s">
-        <v>6</v>
-      </c>
-      <c r="F21" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6">
-      <c r="A22">
-        <v>20330051920153</v>
-      </c>
-      <c r="B22" t="s">
-        <v>76</v>
-      </c>
-      <c r="D22" t="s">
-        <v>98</v>
-      </c>
-      <c r="E22" t="s">
-        <v>6</v>
-      </c>
-      <c r="F22" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4293,16 +4156,16 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920122</v>
+        <v>20330051920148</v>
       </c>
       <c r="B2" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="C2" t="s">
-        <v>77</v>
+        <v>81</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E2">
         <v>3</v>
@@ -4310,33 +4173,33 @@
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920148</v>
+        <v>20330051920122</v>
       </c>
       <c r="B3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C3" t="s">
         <v>74</v>
       </c>
-      <c r="C3" t="s">
-        <v>86</v>
-      </c>
       <c r="D3" t="s">
-        <v>96</v>
+        <v>83</v>
       </c>
       <c r="E3">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920126</v>
+        <v>20330051920136</v>
       </c>
       <c r="B4" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4344,16 +4207,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920135</v>
+        <v>20330051920144</v>
       </c>
       <c r="B5" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4361,67 +4224,67 @@
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920136</v>
+        <v>20330051920126</v>
       </c>
       <c r="B6" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C6" t="s">
-        <v>82</v>
+        <v>75</v>
       </c>
       <c r="D6" t="s">
-        <v>92</v>
+        <v>84</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920144</v>
+        <v>20330051920135</v>
       </c>
       <c r="B7" t="s">
-        <v>72</v>
+        <v>67</v>
       </c>
       <c r="C7" t="s">
+        <v>76</v>
+      </c>
+      <c r="D7" t="s">
         <v>84</v>
       </c>
-      <c r="D7" t="s">
-        <v>94</v>
-      </c>
       <c r="E7">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920151</v>
+        <v>20330051920141</v>
       </c>
       <c r="B8" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="C8" t="s">
-        <v>87</v>
+        <v>78</v>
       </c>
       <c r="D8" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="E8">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920123</v>
+        <v>20330051920387</v>
       </c>
       <c r="B9" t="s">
-        <v>66</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4429,16 +4292,16 @@
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920129</v>
+        <v>20330051920151</v>
       </c>
       <c r="B10" t="s">
-        <v>68</v>
+        <v>73</v>
       </c>
       <c r="C10" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="D10" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E10">
         <v>1</v>
@@ -4446,64 +4309,67 @@
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920141</v>
+        <v>20330051920115</v>
       </c>
       <c r="B11" t="s">
-        <v>71</v>
+        <v>91</v>
       </c>
       <c r="C11" t="s">
-        <v>83</v>
+        <v>65</v>
       </c>
       <c r="D11" t="s">
-        <v>93</v>
+        <v>126</v>
       </c>
       <c r="E11">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920387</v>
+        <v>20330051920116</v>
       </c>
       <c r="B12" t="s">
-        <v>73</v>
+        <v>92</v>
       </c>
       <c r="C12" t="s">
-        <v>85</v>
+        <v>111</v>
       </c>
       <c r="D12" t="s">
-        <v>95</v>
+        <v>127</v>
       </c>
       <c r="E12">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920153</v>
+        <v>20330051920118</v>
       </c>
       <c r="B13" t="s">
-        <v>76</v>
+        <v>93</v>
+      </c>
+      <c r="C13" t="s">
+        <v>75</v>
       </c>
       <c r="D13" t="s">
-        <v>98</v>
+        <v>128</v>
       </c>
       <c r="E13">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920115</v>
+        <v>20330051920119</v>
       </c>
       <c r="B14" t="s">
-        <v>99</v>
+        <v>94</v>
       </c>
       <c r="C14" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D14" t="s">
-        <v>129</v>
+        <v>88</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4511,16 +4377,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920116</v>
+        <v>20330051920121</v>
       </c>
       <c r="B15" t="s">
-        <v>100</v>
+        <v>95</v>
       </c>
       <c r="C15" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="D15" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4528,16 +4394,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920118</v>
+        <v>20330051920123</v>
       </c>
       <c r="B16" t="s">
-        <v>101</v>
+        <v>96</v>
       </c>
       <c r="C16" t="s">
-        <v>79</v>
+        <v>113</v>
       </c>
       <c r="D16" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4545,16 +4411,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920119</v>
+        <v>20330051920124</v>
       </c>
       <c r="B17" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
       <c r="C17" t="s">
-        <v>67</v>
+        <v>114</v>
       </c>
       <c r="D17" t="s">
-        <v>95</v>
+        <v>131</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4562,13 +4428,13 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920121</v>
+        <v>20330051920125</v>
       </c>
       <c r="B18" t="s">
-        <v>103</v>
+        <v>75</v>
       </c>
       <c r="C18" t="s">
-        <v>117</v>
+        <v>66</v>
       </c>
       <c r="D18" t="s">
         <v>132</v>
@@ -4579,13 +4445,13 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920124</v>
+        <v>20330051920127</v>
       </c>
       <c r="B19" t="s">
         <v>66</v>
       </c>
       <c r="C19" t="s">
-        <v>118</v>
+        <v>66</v>
       </c>
       <c r="D19" t="s">
         <v>133</v>
@@ -4596,13 +4462,13 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920125</v>
+        <v>20330051920128</v>
       </c>
       <c r="B20" t="s">
-        <v>79</v>
+        <v>66</v>
       </c>
       <c r="C20" t="s">
-        <v>67</v>
+        <v>115</v>
       </c>
       <c r="D20" t="s">
         <v>134</v>
@@ -4613,13 +4479,13 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920127</v>
+        <v>20330051920129</v>
       </c>
       <c r="B21" t="s">
-        <v>67</v>
+        <v>97</v>
       </c>
       <c r="C21" t="s">
-        <v>67</v>
+        <v>116</v>
       </c>
       <c r="D21" t="s">
         <v>135</v>
@@ -4630,13 +4496,13 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920128</v>
+        <v>20330051920131</v>
       </c>
       <c r="B22" t="s">
-        <v>67</v>
+        <v>98</v>
       </c>
       <c r="C22" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D22" t="s">
         <v>136</v>
@@ -4647,13 +4513,13 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920131</v>
+        <v>20330051920132</v>
       </c>
       <c r="B23" t="s">
-        <v>104</v>
+        <v>99</v>
       </c>
       <c r="C23" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D23" t="s">
         <v>137</v>
@@ -4664,13 +4530,13 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920132</v>
+        <v>20330051920133</v>
       </c>
       <c r="B24" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="C24" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D24" t="s">
         <v>138</v>
@@ -4681,13 +4547,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920133</v>
+        <v>20330051920134</v>
       </c>
       <c r="B25" t="s">
-        <v>105</v>
+        <v>100</v>
       </c>
       <c r="C25" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4698,13 +4564,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920134</v>
+        <v>20330051920137</v>
       </c>
       <c r="B26" t="s">
-        <v>106</v>
+        <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4715,13 +4581,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920137</v>
+        <v>20330051920139</v>
       </c>
       <c r="B27" t="s">
-        <v>107</v>
+        <v>77</v>
       </c>
       <c r="C27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4732,13 +4598,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>20330051920139</v>
+        <v>19330051920387</v>
       </c>
       <c r="B28" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
       <c r="C28" t="s">
-        <v>125</v>
+        <v>96</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4749,16 +4615,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>19330051920387</v>
+        <v>20330051920140</v>
       </c>
       <c r="B29" t="s">
-        <v>108</v>
+        <v>103</v>
       </c>
       <c r="C29" t="s">
-        <v>66</v>
+        <v>76</v>
       </c>
       <c r="D29" t="s">
-        <v>143</v>
+        <v>88</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4766,16 +4632,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920140</v>
+        <v>20330051920389</v>
       </c>
       <c r="B30" t="s">
-        <v>109</v>
+        <v>104</v>
       </c>
       <c r="C30" t="s">
-        <v>81</v>
+        <v>123</v>
       </c>
       <c r="D30" t="s">
-        <v>95</v>
+        <v>143</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4783,13 +4649,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920389</v>
+        <v>20330051920142</v>
       </c>
       <c r="B31" t="s">
-        <v>110</v>
+        <v>105</v>
       </c>
       <c r="C31" t="s">
-        <v>126</v>
+        <v>119</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -4800,13 +4666,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920142</v>
+        <v>20330051920143</v>
       </c>
       <c r="B32" t="s">
-        <v>111</v>
+        <v>106</v>
       </c>
       <c r="C32" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -4817,13 +4683,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920143</v>
+        <v>20330051920145</v>
       </c>
       <c r="B33" t="s">
-        <v>112</v>
+        <v>107</v>
       </c>
       <c r="C33" t="s">
-        <v>127</v>
+        <v>99</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4834,13 +4700,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920145</v>
+        <v>20330051920150</v>
       </c>
       <c r="B34" t="s">
-        <v>113</v>
+        <v>108</v>
       </c>
       <c r="C34" t="s">
-        <v>105</v>
+        <v>125</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -4851,13 +4717,10 @@
     </row>
     <row r="35" spans="1:5">
       <c r="A35">
-        <v>20330051920150</v>
+        <v>20330051920153</v>
       </c>
       <c r="B35" t="s">
-        <v>114</v>
-      </c>
-      <c r="C35" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -4871,10 +4734,10 @@
         <v>20330051920154</v>
       </c>
       <c r="B36" t="s">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="C36" t="s">
-        <v>100</v>
+        <v>92</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -4890,7 +4753,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G10"/>
+  <dimension ref="A1:G4"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4922,45 +4785,45 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920136</v>
+        <v>20330051920151</v>
       </c>
       <c r="B2" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
         <v>82</v>
       </c>
       <c r="D2" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E2" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="F2" t="s">
-        <v>55</v>
+        <v>60</v>
       </c>
       <c r="G2">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920136</v>
+        <v>20330051920151</v>
       </c>
       <c r="B3" t="s">
-        <v>70</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
         <v>82</v>
       </c>
       <c r="D3" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
       </c>
       <c r="F3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="G3">
         <v>-1</v>
@@ -4968,160 +4831,25 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920151</v>
+        <v>20330051920119</v>
       </c>
       <c r="B4" t="s">
-        <v>75</v>
+        <v>94</v>
       </c>
       <c r="C4" t="s">
-        <v>87</v>
+        <v>66</v>
       </c>
       <c r="D4" t="s">
-        <v>97</v>
+        <v>88</v>
       </c>
       <c r="E4" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>55</v>
+        <v>59</v>
       </c>
       <c r="G4">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="A5">
-        <v>20330051920151</v>
-      </c>
-      <c r="B5" t="s">
-        <v>75</v>
-      </c>
-      <c r="C5" t="s">
-        <v>87</v>
-      </c>
-      <c r="D5" t="s">
-        <v>97</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>56</v>
-      </c>
-      <c r="G5">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="A6">
-        <v>20330051920119</v>
-      </c>
-      <c r="B6" t="s">
-        <v>102</v>
-      </c>
-      <c r="C6" t="s">
-        <v>67</v>
-      </c>
-      <c r="D6" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" t="s">
-        <v>7</v>
-      </c>
-      <c r="F6" t="s">
-        <v>60</v>
-      </c>
-      <c r="G6">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="A7">
-        <v>20330051920123</v>
-      </c>
-      <c r="B7" t="s">
-        <v>66</v>
-      </c>
-      <c r="C7" t="s">
-        <v>78</v>
-      </c>
-      <c r="D7" t="s">
-        <v>89</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>55</v>
-      </c>
-      <c r="G7">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7">
-      <c r="A8">
-        <v>20330051920129</v>
-      </c>
-      <c r="B8" t="s">
-        <v>68</v>
-      </c>
-      <c r="C8" t="s">
-        <v>80</v>
-      </c>
-      <c r="D8" t="s">
-        <v>91</v>
-      </c>
-      <c r="E8" t="s">
-        <v>6</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-      <c r="G8">
-        <v>-1</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7">
-      <c r="A9">
-        <v>20330051920134</v>
-      </c>
-      <c r="B9" t="s">
-        <v>106</v>
-      </c>
-      <c r="C9" t="s">
-        <v>123</v>
-      </c>
-      <c r="D9" t="s">
-        <v>140</v>
-      </c>
-      <c r="E9" t="s">
-        <v>5</v>
-      </c>
-      <c r="F9" t="s">
-        <v>57</v>
-      </c>
-      <c r="G9">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7">
-      <c r="A10">
-        <v>20330051920153</v>
-      </c>
-      <c r="B10" t="s">
-        <v>76</v>
-      </c>
-      <c r="D10" t="s">
-        <v>98</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>55</v>
-      </c>
-      <c r="G10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>

--- a/grupos/3ARHV - Estadisticos 20211.xlsx
+++ b/grupos/3ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -197,10 +197,10 @@
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
     <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
-    <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
     <t>NC</t>
@@ -980,7 +980,7 @@
         <v>8</v>
       </c>
       <c r="K4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L4">
         <v>8</v>
@@ -1057,7 +1057,7 @@
         <v>9</v>
       </c>
       <c r="K5">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L5">
         <v>8</v>
@@ -1134,7 +1134,7 @@
         <v>9</v>
       </c>
       <c r="K6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L6">
         <v>10</v>
@@ -1211,7 +1211,7 @@
         <v>-1</v>
       </c>
       <c r="K7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L7">
         <v>6</v>
@@ -1247,7 +1247,7 @@
         <v>5</v>
       </c>
       <c r="W7">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X7">
         <v>7</v>
@@ -1288,7 +1288,7 @@
         <v>8</v>
       </c>
       <c r="K8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L8">
         <v>9</v>
@@ -1365,7 +1365,7 @@
         <v>9</v>
       </c>
       <c r="K9">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L9">
         <v>6</v>
@@ -1401,7 +1401,7 @@
         <v>8</v>
       </c>
       <c r="W9">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X9">
         <v>5</v>
@@ -1519,7 +1519,7 @@
         <v>9</v>
       </c>
       <c r="K11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L11">
         <v>9</v>
@@ -1596,7 +1596,7 @@
         <v>9</v>
       </c>
       <c r="K12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L12">
         <v>6</v>
@@ -1632,7 +1632,7 @@
         <v>8</v>
       </c>
       <c r="W12">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X12">
         <v>7</v>
@@ -1673,7 +1673,7 @@
         <v>8</v>
       </c>
       <c r="K13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L13">
         <v>9</v>
@@ -1709,7 +1709,7 @@
         <v>9</v>
       </c>
       <c r="W13">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X13">
         <v>9</v>
@@ -1827,7 +1827,7 @@
         <v>8</v>
       </c>
       <c r="K15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L15">
         <v>7</v>
@@ -1904,7 +1904,7 @@
         <v>10</v>
       </c>
       <c r="K16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L16">
         <v>9</v>
@@ -1981,7 +1981,7 @@
         <v>9</v>
       </c>
       <c r="K17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L17">
         <v>8</v>
@@ -2017,7 +2017,7 @@
         <v>10</v>
       </c>
       <c r="W17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X17">
         <v>8</v>
@@ -2058,7 +2058,7 @@
         <v>9</v>
       </c>
       <c r="K18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L18">
         <v>9</v>
@@ -2094,7 +2094,7 @@
         <v>9</v>
       </c>
       <c r="W18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X18">
         <v>9</v>
@@ -2135,7 +2135,7 @@
         <v>9</v>
       </c>
       <c r="K19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L19">
         <v>7</v>
@@ -2171,7 +2171,7 @@
         <v>9</v>
       </c>
       <c r="W19">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2209,7 +2209,7 @@
         <v>-1</v>
       </c>
       <c r="J20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K20">
         <v>-1</v>
@@ -2289,7 +2289,7 @@
         <v>8</v>
       </c>
       <c r="K21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L21">
         <v>5</v>
@@ -2325,7 +2325,7 @@
         <v>9</v>
       </c>
       <c r="W21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X21">
         <v>5</v>
@@ -2437,13 +2437,13 @@
         <v>9</v>
       </c>
       <c r="I23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="K23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L23">
         <v>9</v>
@@ -2473,7 +2473,7 @@
         <v>7</v>
       </c>
       <c r="U23">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2514,13 +2514,13 @@
         <v>10</v>
       </c>
       <c r="I24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J24">
         <v>9</v>
       </c>
       <c r="K24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L24">
         <v>9</v>
@@ -2556,7 +2556,7 @@
         <v>9</v>
       </c>
       <c r="W24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="X24">
         <v>9</v>
@@ -2597,7 +2597,7 @@
         <v>8</v>
       </c>
       <c r="K25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L25">
         <v>10</v>
@@ -2633,7 +2633,7 @@
         <v>9</v>
       </c>
       <c r="W25">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X25">
         <v>10</v>
@@ -2668,13 +2668,13 @@
         <v>8</v>
       </c>
       <c r="I26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J26">
         <v>8</v>
       </c>
       <c r="K26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L26">
         <v>6</v>
@@ -2751,7 +2751,7 @@
         <v>9</v>
       </c>
       <c r="K27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L27">
         <v>10</v>
@@ -2905,7 +2905,7 @@
         <v>9</v>
       </c>
       <c r="K29">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="L29">
         <v>8</v>
@@ -2982,7 +2982,7 @@
         <v>9</v>
       </c>
       <c r="K30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L30">
         <v>10</v>
@@ -3059,7 +3059,7 @@
         <v>10</v>
       </c>
       <c r="K31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L31">
         <v>9</v>
@@ -3095,7 +3095,7 @@
         <v>10</v>
       </c>
       <c r="W31">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X31">
         <v>9</v>
@@ -3136,7 +3136,7 @@
         <v>9</v>
       </c>
       <c r="K32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L32">
         <v>6</v>
@@ -3172,7 +3172,7 @@
         <v>9</v>
       </c>
       <c r="W32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X32">
         <v>5</v>
@@ -3213,7 +3213,7 @@
         <v>9</v>
       </c>
       <c r="K33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="L33">
         <v>8</v>
@@ -3269,7 +3269,7 @@
         <v>-1</v>
       </c>
       <c r="D34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="E34">
         <v>5</v>
@@ -3287,10 +3287,10 @@
         <v>-1</v>
       </c>
       <c r="J34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="K34">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L34">
         <v>6</v>
@@ -3323,7 +3323,7 @@
         <v>-1</v>
       </c>
       <c r="V34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="W34">
         <v>5</v>
@@ -3367,7 +3367,7 @@
         <v>8</v>
       </c>
       <c r="K35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L35">
         <v>10</v>
@@ -3403,7 +3403,7 @@
         <v>9</v>
       </c>
       <c r="W35">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="X35">
         <v>10</v>
@@ -3444,7 +3444,7 @@
         <v>-1</v>
       </c>
       <c r="K36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L36">
         <v>6</v>
@@ -3521,7 +3521,7 @@
         <v>8</v>
       </c>
       <c r="K37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="L37">
         <v>10</v>
@@ -3557,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3692,19 +3692,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="E4">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="F4">
-        <v>82.86</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G4">
-        <v>17.14</v>
+        <v>11.43</v>
       </c>
       <c r="H4">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3736,7 +3736,7 @@
         <v>0</v>
       </c>
       <c r="H5">
-        <v>9.9</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="I5">
         <v>4</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3759,27 +3759,27 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6">
         <v>91.43000000000001</v>
       </c>
       <c r="G6">
-        <v>5.71</v>
+        <v>8.57</v>
       </c>
       <c r="H6">
-        <v>8.5</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>2.86</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -3788,19 +3788,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E7">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F7">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G7">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="H7">
-        <v>8.199999999999999</v>
+        <v>8.5</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3816,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F15"/>
+  <dimension ref="A1:F14"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4057,10 +4057,10 @@
         <v>89</v>
       </c>
       <c r="E12" t="s">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F12" t="s">
-        <v>59</v>
+        <v>55</v>
       </c>
     </row>
     <row r="13" spans="1:6">
@@ -4077,49 +4077,29 @@
         <v>89</v>
       </c>
       <c r="E13" t="s">
-        <v>10</v>
+        <v>6</v>
       </c>
       <c r="F13" t="s">
-        <v>55</v>
+        <v>58</v>
       </c>
     </row>
     <row r="14" spans="1:6">
       <c r="A14">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B14" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C14" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D14" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E14" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F14" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6">
-      <c r="A15">
-        <v>20330051920151</v>
-      </c>
-      <c r="B15" t="s">
-        <v>73</v>
-      </c>
-      <c r="C15" t="s">
-        <v>82</v>
-      </c>
-      <c r="D15" t="s">
-        <v>90</v>
-      </c>
-      <c r="E15" t="s">
-        <v>10</v>
-      </c>
-      <c r="F15" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4156,33 +4136,33 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920148</v>
+        <v>20330051920122</v>
       </c>
       <c r="B2" t="s">
-        <v>72</v>
+        <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>81</v>
+        <v>74</v>
       </c>
       <c r="D2" t="s">
-        <v>89</v>
+        <v>83</v>
       </c>
       <c r="E2">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920122</v>
+        <v>20330051920136</v>
       </c>
       <c r="B3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
       <c r="C3" t="s">
-        <v>74</v>
+        <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="E3">
         <v>2</v>
@@ -4190,16 +4170,16 @@
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920136</v>
+        <v>20330051920144</v>
       </c>
       <c r="B4" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C4" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="D4" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="E4">
         <v>2</v>
@@ -4207,16 +4187,16 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920144</v>
+        <v>20330051920148</v>
       </c>
       <c r="B5" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C5" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="D5" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="E5">
         <v>2</v>
@@ -4753,7 +4733,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G4"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4785,22 +4765,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920151</v>
+        <v>20330051920387</v>
       </c>
       <c r="B2" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C2" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D2" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E2" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4808,16 +4788,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920151</v>
+        <v>20330051920387</v>
       </c>
       <c r="B3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="C3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4831,24 +4811,70 @@
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920119</v>
+        <v>20330051920151</v>
       </c>
       <c r="B4" t="s">
-        <v>94</v>
+        <v>73</v>
       </c>
       <c r="C4" t="s">
-        <v>66</v>
+        <v>82</v>
       </c>
       <c r="D4" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="E4" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F4" t="s">
         <v>59</v>
       </c>
       <c r="G4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7">
+      <c r="A5">
+        <v>20330051920151</v>
+      </c>
+      <c r="B5" t="s">
+        <v>73</v>
+      </c>
+      <c r="C5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D5" t="s">
+        <v>90</v>
+      </c>
+      <c r="E5" t="s">
+        <v>10</v>
+      </c>
+      <c r="F5" t="s">
+        <v>55</v>
+      </c>
+      <c r="G5">
+        <v>-1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7">
+      <c r="A6">
+        <v>20330051920119</v>
+      </c>
+      <c r="B6" t="s">
+        <v>94</v>
+      </c>
+      <c r="C6" t="s">
+        <v>66</v>
+      </c>
+      <c r="D6" t="s">
+        <v>88</v>
+      </c>
+      <c r="E6" t="s">
+        <v>7</v>
+      </c>
+      <c r="F6" t="s">
+        <v>60</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
     </row>

--- a/grupos/3ARHV - Estadisticos 20211.xlsx
+++ b/grupos/3ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -194,10 +194,10 @@
     <t>González Nuñez Veronica</t>
   </si>
   <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
     <t>Molina Quezada Raúl</t>
-  </si>
-  <si>
-    <t>Camarillo Aburto Raymundo</t>
   </si>
   <si>
     <t>Muñoz Rivadeneyra Salvador</t>
@@ -1208,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="J7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K7">
         <v>6</v>
@@ -1667,7 +1667,7 @@
         <v>10</v>
       </c>
       <c r="I13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="J13">
         <v>8</v>
@@ -1747,7 +1747,7 @@
         <v>-1</v>
       </c>
       <c r="J14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K14">
         <v>-1</v>
@@ -1783,7 +1783,7 @@
         <v>10</v>
       </c>
       <c r="V14">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W14">
         <v>5</v>
@@ -2206,7 +2206,7 @@
         <v>9</v>
       </c>
       <c r="I20">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J20">
         <v>7</v>
@@ -2242,7 +2242,7 @@
         <v>9</v>
       </c>
       <c r="U20">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V20">
         <v>8</v>
@@ -2363,7 +2363,7 @@
         <v>-1</v>
       </c>
       <c r="J22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K22">
         <v>-1</v>
@@ -2399,7 +2399,7 @@
         <v>10</v>
       </c>
       <c r="V22">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2825,7 +2825,7 @@
         <v>-1</v>
       </c>
       <c r="J28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K28">
         <v>-1</v>
@@ -3266,7 +3266,7 @@
         <v>5</v>
       </c>
       <c r="C34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="D34">
         <v>8</v>
@@ -3284,7 +3284,7 @@
         <v>8</v>
       </c>
       <c r="I34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="J34">
         <v>8</v>
@@ -3320,7 +3320,7 @@
         <v>7</v>
       </c>
       <c r="U34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="V34">
         <v>8</v>
@@ -3441,7 +3441,7 @@
         <v>9</v>
       </c>
       <c r="J36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="K36">
         <v>6</v>
@@ -3477,7 +3477,7 @@
         <v>10</v>
       </c>
       <c r="V36">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W36">
         <v>7</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3724,30 +3724,30 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E5">
+        <v>3</v>
+      </c>
+      <c r="F5">
+        <v>91.43000000000001</v>
+      </c>
+      <c r="G5">
+        <v>8.57</v>
+      </c>
+      <c r="H5">
+        <v>8.199999999999999</v>
+      </c>
+      <c r="I5">
         <v>0</v>
       </c>
-      <c r="F5">
-        <v>88.56999999999999</v>
-      </c>
-      <c r="G5">
+      <c r="J5">
         <v>0</v>
-      </c>
-      <c r="H5">
-        <v>9.800000000000001</v>
-      </c>
-      <c r="I5">
-        <v>4</v>
-      </c>
-      <c r="J5">
-        <v>11.43</v>
       </c>
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3759,22 +3759,22 @@
         <v>32</v>
       </c>
       <c r="E6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F6">
         <v>91.43000000000001</v>
       </c>
       <c r="G6">
+        <v>0</v>
+      </c>
+      <c r="H6">
+        <v>9.800000000000001</v>
+      </c>
+      <c r="I6">
+        <v>3</v>
+      </c>
+      <c r="J6">
         <v>8.57</v>
-      </c>
-      <c r="H6">
-        <v>8.199999999999999</v>
-      </c>
-      <c r="I6">
-        <v>0</v>
-      </c>
-      <c r="J6">
-        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3800,7 +3800,7 @@
         <v>5.71</v>
       </c>
       <c r="H7">
-        <v>8.5</v>
+        <v>8.4</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3816,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F14"/>
+  <dimension ref="A1:F13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3880,7 +3880,7 @@
         <v>6</v>
       </c>
       <c r="F3" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="4" spans="1:6">
@@ -3960,7 +3960,7 @@
         <v>6</v>
       </c>
       <c r="F7" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:6">
@@ -4020,7 +4020,7 @@
         <v>6</v>
       </c>
       <c r="F10" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
     </row>
     <row r="11" spans="1:6">
@@ -4065,41 +4065,21 @@
     </row>
     <row r="13" spans="1:6">
       <c r="A13">
-        <v>20330051920148</v>
+        <v>20330051920151</v>
       </c>
       <c r="B13" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="D13" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="E13" t="s">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="F13" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6">
-      <c r="A14">
-        <v>20330051920151</v>
-      </c>
-      <c r="B14" t="s">
-        <v>73</v>
-      </c>
-      <c r="C14" t="s">
-        <v>82</v>
-      </c>
-      <c r="D14" t="s">
-        <v>90</v>
-      </c>
-      <c r="E14" t="s">
-        <v>10</v>
-      </c>
-      <c r="F14" t="s">
         <v>55</v>
       </c>
     </row>
@@ -4187,30 +4167,30 @@
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920148</v>
+        <v>20330051920126</v>
       </c>
       <c r="B5" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="C5" t="s">
-        <v>81</v>
+        <v>75</v>
       </c>
       <c r="D5" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="E5">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920126</v>
+        <v>20330051920135</v>
       </c>
       <c r="B6" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C6" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="D6" t="s">
         <v>84</v>
@@ -4221,16 +4201,16 @@
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920135</v>
+        <v>20330051920141</v>
       </c>
       <c r="B7" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C7" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="D7" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="E7">
         <v>1</v>
@@ -4238,16 +4218,16 @@
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920141</v>
+        <v>20330051920387</v>
       </c>
       <c r="B8" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="D8" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="E8">
         <v>1</v>
@@ -4255,16 +4235,16 @@
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920387</v>
+        <v>20330051920148</v>
       </c>
       <c r="B9" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="C9" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D9" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="E9">
         <v>1</v>
@@ -4826,7 +4806,7 @@
         <v>5</v>
       </c>
       <c r="F4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="G4">
         <v>5</v>

--- a/grupos/3ARHV - Estadisticos 20211.xlsx
+++ b/grupos/3ARHV - Estadisticos 20211.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="293" uniqueCount="150">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="243" uniqueCount="150">
   <si>
     <t>Materia</t>
   </si>
@@ -188,21 +188,21 @@
     <t>Hernández Mendoza Delfina</t>
   </si>
   <si>
+    <t>Camarillo Aburto Raymundo</t>
+  </si>
+  <si>
+    <t>Muñoz Rivadeneyra Salvador</t>
+  </si>
+  <si>
     <t>Mendoza Velazquez Laura Elena</t>
   </si>
   <si>
     <t>González Nuñez Veronica</t>
   </si>
   <si>
-    <t>Camarillo Aburto Raymundo</t>
-  </si>
-  <si>
     <t>Molina Quezada Raúl</t>
   </si>
   <si>
-    <t>Muñoz Rivadeneyra Salvador</t>
-  </si>
-  <si>
     <t>NC</t>
   </si>
   <si>
@@ -215,48 +215,150 @@
     <t>Nombres</t>
   </si>
   <si>
+    <t>CASTELLANOS</t>
+  </si>
+  <si>
+    <t>CARRERA</t>
+  </si>
+  <si>
+    <t>CONGUILLO</t>
+  </si>
+  <si>
+    <t>CORONA</t>
+  </si>
+  <si>
+    <t>CUATRA</t>
+  </si>
+  <si>
     <t>FLORES</t>
   </si>
   <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>GONZALEZ</t>
+  </si>
+  <si>
     <t>HERNANDEZ</t>
   </si>
   <si>
+    <t>JIMENEZ</t>
+  </si>
+  <si>
+    <t>LIMON</t>
+  </si>
+  <si>
+    <t>LOPEZ</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
     <t>MARROQUIN</t>
   </si>
   <si>
     <t>MARCIAL</t>
   </si>
   <si>
+    <t>MAYAHUA</t>
+  </si>
+  <si>
+    <t>MORALES</t>
+  </si>
+  <si>
+    <t>OLTEHUA</t>
+  </si>
+  <si>
+    <t>OLIVARES</t>
+  </si>
+  <si>
     <t>OSORIO</t>
   </si>
   <si>
+    <t>PACHECO</t>
+  </si>
+  <si>
+    <t>RIVERA</t>
+  </si>
+  <si>
+    <t>RODRIGUEZ</t>
+  </si>
+  <si>
     <t>DE LA ROSA</t>
   </si>
   <si>
     <t>ROSAS</t>
   </si>
   <si>
+    <t>RUIZ</t>
+  </si>
+  <si>
     <t>SANCHEZ</t>
   </si>
   <si>
+    <t>TIBURCIO</t>
+  </si>
+  <si>
     <t>TORRES</t>
   </si>
   <si>
+    <t>TRUJILLO</t>
+  </si>
+  <si>
+    <t>VELAZQEZ</t>
+  </si>
+  <si>
+    <t>ROMANOS</t>
+  </si>
+  <si>
+    <t>ZOPIYACTLE</t>
+  </si>
+  <si>
     <t>CERVANTES</t>
   </si>
   <si>
-    <t>GONZALEZ</t>
+    <t>JUAREZ</t>
+  </si>
+  <si>
+    <t>SANTIAGO</t>
+  </si>
+  <si>
+    <t>SUAREZ</t>
+  </si>
+  <si>
+    <t>APARICIO</t>
+  </si>
+  <si>
+    <t>BASILIO</t>
+  </si>
+  <si>
+    <t>NOYOLA</t>
+  </si>
+  <si>
+    <t>ROMERO</t>
+  </si>
+  <si>
+    <t>CHIPAHUA</t>
   </si>
   <si>
     <t>HERRERA</t>
   </si>
   <si>
-    <t>MORALES</t>
+    <t>XOCHIQUISQUI</t>
+  </si>
+  <si>
+    <t>REYNOSO</t>
   </si>
   <si>
     <t>MACHORRO</t>
   </si>
   <si>
+    <t>MAZAHUA</t>
+  </si>
+  <si>
+    <t>BARRAGAN</t>
+  </si>
+  <si>
     <t>CASTRO</t>
   </si>
   <si>
@@ -266,202 +368,100 @@
     <t>RAMON</t>
   </si>
   <si>
+    <t>ORTEGA</t>
+  </si>
+  <si>
     <t>PEREZ</t>
   </si>
   <si>
+    <t>MELANIE NAOMI</t>
+  </si>
+  <si>
+    <t>AMARANTA DENISSE</t>
+  </si>
+  <si>
+    <t>CONSUELO DALILA</t>
+  </si>
+  <si>
+    <t>MARIA FERNANDA</t>
+  </si>
+  <si>
+    <t>MARIA</t>
+  </si>
+  <si>
     <t>JAVIER</t>
   </si>
   <si>
+    <t>EMELIN JIROMI</t>
+  </si>
+  <si>
+    <t>ITZEL</t>
+  </si>
+  <si>
+    <t>AIDA</t>
+  </si>
+  <si>
     <t>ESMERALDA</t>
   </si>
   <si>
+    <t>ODALYS</t>
+  </si>
+  <si>
+    <t>KIMBERLY ALONDRA</t>
+  </si>
+  <si>
+    <t>YAZMIN</t>
+  </si>
+  <si>
+    <t>MARIJOSE</t>
+  </si>
+  <si>
+    <t>MARIA JOSE</t>
+  </si>
+  <si>
+    <t>ABDIEL</t>
+  </si>
+  <si>
+    <t>GERMAN ERNESTO</t>
+  </si>
+  <si>
     <t>IVAN DE JESUS</t>
   </si>
   <si>
+    <t>DAMARIS</t>
+  </si>
+  <si>
+    <t>VALERIA</t>
+  </si>
+  <si>
+    <t>SANDY SAMARA</t>
+  </si>
+  <si>
     <t>KARLA</t>
   </si>
   <si>
+    <t>TAILY</t>
+  </si>
+  <si>
+    <t>INGRID YALITH</t>
+  </si>
+  <si>
+    <t>LUCERO</t>
+  </si>
+  <si>
     <t>ALONDRA</t>
   </si>
   <si>
-    <t>MARIA FERNANDA</t>
+    <t>XIMENA MICHELL</t>
   </si>
   <si>
     <t>MEILYN ADABEL</t>
   </si>
   <si>
+    <t>DIANA VIANNEY</t>
+  </si>
+  <si>
     <t>CONSTANZA XIMENA</t>
-  </si>
-  <si>
-    <t>CASTELLANOS</t>
-  </si>
-  <si>
-    <t>CARRERA</t>
-  </si>
-  <si>
-    <t>CONGUILLO</t>
-  </si>
-  <si>
-    <t>CORONA</t>
-  </si>
-  <si>
-    <t>CUATRA</t>
-  </si>
-  <si>
-    <t>GARCIA</t>
-  </si>
-  <si>
-    <t>JIMENEZ</t>
-  </si>
-  <si>
-    <t>LIMON</t>
-  </si>
-  <si>
-    <t>LOPEZ</t>
-  </si>
-  <si>
-    <t>MARTINEZ</t>
-  </si>
-  <si>
-    <t>MAYAHUA</t>
-  </si>
-  <si>
-    <t>OLTEHUA</t>
-  </si>
-  <si>
-    <t>OLIVARES</t>
-  </si>
-  <si>
-    <t>PACHECO</t>
-  </si>
-  <si>
-    <t>RIVERA</t>
-  </si>
-  <si>
-    <t>RODRIGUEZ</t>
-  </si>
-  <si>
-    <t>RUIZ</t>
-  </si>
-  <si>
-    <t>TIBURCIO</t>
-  </si>
-  <si>
-    <t>TRUJILLO</t>
-  </si>
-  <si>
-    <t>VELAZQEZ</t>
-  </si>
-  <si>
-    <t>ROMANOS</t>
-  </si>
-  <si>
-    <t>ZOPIYACTLE</t>
-  </si>
-  <si>
-    <t>JUAREZ</t>
-  </si>
-  <si>
-    <t>SANTIAGO</t>
-  </si>
-  <si>
-    <t>SUAREZ</t>
-  </si>
-  <si>
-    <t>APARICIO</t>
-  </si>
-  <si>
-    <t>BASILIO</t>
-  </si>
-  <si>
-    <t>NOYOLA</t>
-  </si>
-  <si>
-    <t>ROMERO</t>
-  </si>
-  <si>
-    <t>CHIPAHUA</t>
-  </si>
-  <si>
-    <t>XOCHIQUISQUI</t>
-  </si>
-  <si>
-    <t>REYNOSO</t>
-  </si>
-  <si>
-    <t>MAZAHUA</t>
-  </si>
-  <si>
-    <t>BARRAGAN</t>
-  </si>
-  <si>
-    <t>ORTEGA</t>
-  </si>
-  <si>
-    <t>MELANIE NAOMI</t>
-  </si>
-  <si>
-    <t>AMARANTA DENISSE</t>
-  </si>
-  <si>
-    <t>CONSUELO DALILA</t>
-  </si>
-  <si>
-    <t>MARIA</t>
-  </si>
-  <si>
-    <t>EMELIN JIROMI</t>
-  </si>
-  <si>
-    <t>ITZEL</t>
-  </si>
-  <si>
-    <t>AIDA</t>
-  </si>
-  <si>
-    <t>ODALYS</t>
-  </si>
-  <si>
-    <t>KIMBERLY ALONDRA</t>
-  </si>
-  <si>
-    <t>YAZMIN</t>
-  </si>
-  <si>
-    <t>MARIJOSE</t>
-  </si>
-  <si>
-    <t>MARIA JOSE</t>
-  </si>
-  <si>
-    <t>ABDIEL</t>
-  </si>
-  <si>
-    <t>GERMAN ERNESTO</t>
-  </si>
-  <si>
-    <t>DAMARIS</t>
-  </si>
-  <si>
-    <t>VALERIA</t>
-  </si>
-  <si>
-    <t>SANDY SAMARA</t>
-  </si>
-  <si>
-    <t>TAILY</t>
-  </si>
-  <si>
-    <t>INGRID YALITH</t>
-  </si>
-  <si>
-    <t>LUCERO</t>
-  </si>
-  <si>
-    <t>XIMENA MICHELL</t>
-  </si>
-  <si>
-    <t>DIANA VIANNEY</t>
   </si>
   <si>
     <t>KIMBERLY</t>
@@ -989,28 +989,28 @@
         <v>8</v>
       </c>
       <c r="N4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O4">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P4">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q4">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R4">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S4">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T4">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U4">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V4">
         <v>7</v>
@@ -1019,10 +1019,10 @@
         <v>8</v>
       </c>
       <c r="X4">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y4">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="5" spans="1:25">
@@ -1066,40 +1066,40 @@
         <v>9</v>
       </c>
       <c r="N5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P5">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q5">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S5">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U5">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V5">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W5">
         <v>8</v>
       </c>
       <c r="X5">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y5">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="6" spans="1:25">
@@ -1143,22 +1143,22 @@
         <v>10</v>
       </c>
       <c r="N6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q6">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S6">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T6">
         <v>10</v>
@@ -1167,7 +1167,7 @@
         <v>10</v>
       </c>
       <c r="V6">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W6">
         <v>9</v>
@@ -1220,40 +1220,40 @@
         <v>10</v>
       </c>
       <c r="N7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O7">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q7">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R7">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S7">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T7">
         <v>7</v>
       </c>
       <c r="U7">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V7">
         <v>5</v>
       </c>
       <c r="W7">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X7">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y7">
-        <v>9</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:25">
@@ -1297,25 +1297,25 @@
         <v>9</v>
       </c>
       <c r="N8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q8">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R8">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S8">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T8">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U8">
         <v>9</v>
@@ -1330,7 +1330,7 @@
         <v>9</v>
       </c>
       <c r="Y8">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
     <row r="9" spans="1:25">
@@ -1341,7 +1341,7 @@
         <v>5</v>
       </c>
       <c r="C9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D9">
         <v>7</v>
@@ -1353,13 +1353,13 @@
         <v>5</v>
       </c>
       <c r="G9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H9">
         <v>8</v>
       </c>
       <c r="I9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J9">
         <v>9</v>
@@ -1371,31 +1371,31 @@
         <v>6</v>
       </c>
       <c r="M9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q9">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S9">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T9">
         <v>7</v>
       </c>
       <c r="U9">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V9">
         <v>8</v>
@@ -1404,10 +1404,10 @@
         <v>7</v>
       </c>
       <c r="X9">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y9">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="10" spans="1:25">
@@ -1418,7 +1418,7 @@
         <v>5</v>
       </c>
       <c r="C10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D10">
         <v>5</v>
@@ -1430,61 +1430,61 @@
         <v>5</v>
       </c>
       <c r="G10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H10">
         <v>8</v>
       </c>
       <c r="I10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J10">
         <v>8</v>
       </c>
       <c r="K10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L10">
         <v>6</v>
       </c>
       <c r="M10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P10">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R10">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S10">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T10">
         <v>7</v>
       </c>
       <c r="U10">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V10">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X10">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y10">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="11" spans="1:25">
@@ -1528,28 +1528,28 @@
         <v>10</v>
       </c>
       <c r="N11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P11">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q11">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R11">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S11">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T11">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="U11">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V11">
         <v>8</v>
@@ -1561,7 +1561,7 @@
         <v>8</v>
       </c>
       <c r="Y11">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:25">
@@ -1602,43 +1602,43 @@
         <v>6</v>
       </c>
       <c r="M12">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P12">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R12">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S12">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T12">
         <v>7</v>
       </c>
       <c r="U12">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V12">
         <v>8</v>
       </c>
       <c r="W12">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="X12">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="Y12">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="13" spans="1:25">
@@ -1682,22 +1682,22 @@
         <v>10</v>
       </c>
       <c r="N13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O13">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P13">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R13">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S13">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T13">
         <v>9</v>
@@ -1706,7 +1706,7 @@
         <v>10</v>
       </c>
       <c r="V13">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W13">
         <v>9</v>
@@ -1715,7 +1715,7 @@
         <v>9</v>
       </c>
       <c r="Y13">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="14" spans="1:25">
@@ -1738,61 +1738,61 @@
         <v>5</v>
       </c>
       <c r="G14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H14">
         <v>7</v>
       </c>
       <c r="I14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J14">
         <v>5</v>
       </c>
       <c r="K14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L14">
         <v>5</v>
       </c>
       <c r="M14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N14">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P14">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q14">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R14">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S14">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T14">
         <v>6</v>
       </c>
       <c r="U14">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V14">
         <v>7</v>
       </c>
       <c r="W14">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X14">
         <v>5</v>
       </c>
       <c r="Y14">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="15" spans="1:25">
@@ -1836,40 +1836,40 @@
         <v>7</v>
       </c>
       <c r="N15">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P15">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q15">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R15">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S15">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T15">
         <v>7</v>
       </c>
       <c r="U15">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V15">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W15">
         <v>9</v>
       </c>
       <c r="X15">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="Y15">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="16" spans="1:25">
@@ -1913,40 +1913,40 @@
         <v>7</v>
       </c>
       <c r="N16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q16">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R16">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S16">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="U16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V16">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W16">
         <v>8</v>
       </c>
       <c r="X16">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y16">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="17" spans="1:25">
@@ -1990,31 +1990,31 @@
         <v>10</v>
       </c>
       <c r="N17">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O17">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q17">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S17">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T17">
         <v>9</v>
       </c>
       <c r="U17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V17">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W17">
         <v>9</v>
@@ -2023,7 +2023,7 @@
         <v>8</v>
       </c>
       <c r="Y17">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="18" spans="1:25">
@@ -2067,31 +2067,31 @@
         <v>10</v>
       </c>
       <c r="N18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P18">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S18">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T18">
         <v>10</v>
       </c>
       <c r="U18">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V18">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W18">
         <v>9</v>
@@ -2129,7 +2129,7 @@
         <v>10</v>
       </c>
       <c r="I19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="J19">
         <v>9</v>
@@ -2144,34 +2144,34 @@
         <v>6</v>
       </c>
       <c r="N19">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O19">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P19">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q19">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S19">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T19">
         <v>10</v>
       </c>
       <c r="U19">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V19">
         <v>9</v>
       </c>
       <c r="W19">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X19">
         <v>7</v>
@@ -2212,49 +2212,49 @@
         <v>7</v>
       </c>
       <c r="K20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L20">
         <v>7</v>
       </c>
       <c r="M20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O20">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R20">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S20">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T20">
         <v>9</v>
       </c>
       <c r="U20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V20">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="W20">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X20">
         <v>8</v>
       </c>
       <c r="Y20">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="21" spans="1:25">
@@ -2265,7 +2265,7 @@
         <v>7</v>
       </c>
       <c r="C21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="D21">
         <v>9</v>
@@ -2277,13 +2277,13 @@
         <v>6</v>
       </c>
       <c r="G21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="H21">
         <v>8</v>
       </c>
       <c r="I21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="J21">
         <v>8</v>
@@ -2295,43 +2295,43 @@
         <v>5</v>
       </c>
       <c r="M21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="N21">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="O21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="Q21">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R21">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T21">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="U21">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="V21">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W21">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="X21">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y21">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="22" spans="1:25">
@@ -2354,52 +2354,52 @@
         <v>5</v>
       </c>
       <c r="G22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H22">
         <v>5</v>
       </c>
       <c r="I22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J22">
         <v>5</v>
       </c>
       <c r="K22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="L22">
         <v>6</v>
       </c>
       <c r="M22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q22">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R22">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="S22">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T22">
         <v>5</v>
       </c>
       <c r="U22">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V22">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="W22">
         <v>6</v>
@@ -2408,7 +2408,7 @@
         <v>5</v>
       </c>
       <c r="Y22">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="23" spans="1:25">
@@ -2449,31 +2449,31 @@
         <v>9</v>
       </c>
       <c r="M23">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O23">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q23">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R23">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S23">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="T23">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="U23">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="V23">
         <v>8</v>
@@ -2485,7 +2485,7 @@
         <v>9</v>
       </c>
       <c r="Y23">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="24" spans="1:25">
@@ -2529,28 +2529,28 @@
         <v>7</v>
       </c>
       <c r="N24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="O24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q24">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="S24">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T24">
         <v>9</v>
       </c>
       <c r="U24">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V24">
         <v>9</v>
@@ -2559,7 +2559,7 @@
         <v>9</v>
       </c>
       <c r="X24">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y24">
         <v>8</v>
@@ -2606,22 +2606,22 @@
         <v>9</v>
       </c>
       <c r="N25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R25">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S25">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T25">
         <v>9</v>
@@ -2683,31 +2683,31 @@
         <v>7</v>
       </c>
       <c r="N26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O26">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q26">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R26">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S26">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="T26">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="U26">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V26">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="W26">
         <v>8</v>
@@ -2760,22 +2760,22 @@
         <v>10</v>
       </c>
       <c r="N27">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P27">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R27">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S27">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="T27">
         <v>10</v>
@@ -2784,7 +2784,7 @@
         <v>10</v>
       </c>
       <c r="V27">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W27">
         <v>10</v>
@@ -2793,7 +2793,7 @@
         <v>10</v>
       </c>
       <c r="Y27">
-        <v>10</v>
+        <v>8</v>
       </c>
     </row>
     <row r="28" spans="1:25">
@@ -2816,61 +2816,61 @@
         <v>6</v>
       </c>
       <c r="G28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="H28">
         <v>5</v>
       </c>
       <c r="I28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="J28">
         <v>5</v>
       </c>
       <c r="K28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="L28">
         <v>5</v>
       </c>
       <c r="M28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="O28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="P28">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q28">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R28">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S28">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T28">
         <v>5</v>
       </c>
       <c r="U28">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="V28">
         <v>5</v>
       </c>
       <c r="W28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="X28">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y28">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="29" spans="1:25">
@@ -2914,25 +2914,25 @@
         <v>7</v>
       </c>
       <c r="N29">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R29">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S29">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="T29">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="U29">
         <v>9</v>
@@ -2991,22 +2991,22 @@
         <v>10</v>
       </c>
       <c r="N30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="P30">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S30">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T30">
         <v>10</v>
@@ -3015,7 +3015,7 @@
         <v>10</v>
       </c>
       <c r="V30">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W30">
         <v>10</v>
@@ -3068,31 +3068,31 @@
         <v>10</v>
       </c>
       <c r="N31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O31">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P31">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S31">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T31">
         <v>10</v>
       </c>
       <c r="U31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V31">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="W31">
         <v>10</v>
@@ -3124,7 +3124,7 @@
         <v>5</v>
       </c>
       <c r="G32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H32">
         <v>8</v>
@@ -3142,25 +3142,25 @@
         <v>6</v>
       </c>
       <c r="M32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="N32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="O32">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P32">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="Q32">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="R32">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S32">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="T32">
         <v>7</v>
@@ -3169,16 +3169,16 @@
         <v>10</v>
       </c>
       <c r="V32">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="W32">
         <v>6</v>
       </c>
       <c r="X32">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y32">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="33" spans="1:25">
@@ -3222,28 +3222,28 @@
         <v>9</v>
       </c>
       <c r="N33">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O33">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="P33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R33">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="S33">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T33">
         <v>8</v>
       </c>
       <c r="U33">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="V33">
         <v>9</v>
@@ -3255,7 +3255,7 @@
         <v>8</v>
       </c>
       <c r="Y33">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="34" spans="1:25">
@@ -3278,7 +3278,7 @@
         <v>5</v>
       </c>
       <c r="G34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="H34">
         <v>8</v>
@@ -3296,43 +3296,43 @@
         <v>6</v>
       </c>
       <c r="M34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="N34">
-        <v>-1</v>
+        <v>4</v>
       </c>
       <c r="O34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="P34">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="Q34">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R34">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="S34">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T34">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="U34">
         <v>9</v>
       </c>
       <c r="V34">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="W34">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="X34">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="Y34">
-        <v>-1</v>
+        <v>7</v>
       </c>
     </row>
     <row r="35" spans="1:25">
@@ -3376,22 +3376,22 @@
         <v>10</v>
       </c>
       <c r="N35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="O35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P35">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="R35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S35">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="T35">
         <v>10</v>
@@ -3400,7 +3400,7 @@
         <v>10</v>
       </c>
       <c r="V35">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="W35">
         <v>10</v>
@@ -3432,7 +3432,7 @@
         <v>6</v>
       </c>
       <c r="G36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="H36">
         <v>5</v>
@@ -3450,31 +3450,31 @@
         <v>6</v>
       </c>
       <c r="M36">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="N36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="O36">
-        <v>-1</v>
+        <v>7</v>
       </c>
       <c r="P36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="Q36">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="R36">
-        <v>-1</v>
+        <v>6</v>
       </c>
       <c r="S36">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T36">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="U36">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V36">
         <v>7</v>
@@ -3486,7 +3486,7 @@
         <v>6</v>
       </c>
       <c r="Y36">
-        <v>-1</v>
+        <v>6</v>
       </c>
     </row>
     <row r="37" spans="1:25">
@@ -3530,22 +3530,22 @@
         <v>10</v>
       </c>
       <c r="N37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="O37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="P37">
-        <v>-1</v>
+        <v>9</v>
       </c>
       <c r="Q37">
-        <v>-1</v>
+        <v>5</v>
       </c>
       <c r="R37">
-        <v>-1</v>
+        <v>10</v>
       </c>
       <c r="S37">
-        <v>-1</v>
+        <v>8</v>
       </c>
       <c r="T37">
         <v>10</v>
@@ -3557,7 +3557,7 @@
         <v>9</v>
       </c>
       <c r="W37">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="X37">
         <v>10</v>
@@ -3628,30 +3628,30 @@
         <v>35</v>
       </c>
       <c r="D2">
-        <v>26</v>
+        <v>30</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F2">
-        <v>74.29000000000001</v>
+        <v>85.70999999999999</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>14.29</v>
       </c>
       <c r="H2">
-        <v>8.9</v>
+        <v>7.5</v>
       </c>
       <c r="I2">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="J2">
-        <v>25.71</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>5</v>
       </c>
       <c r="B3" t="s">
         <v>56</v>
@@ -3660,19 +3660,19 @@
         <v>35</v>
       </c>
       <c r="D3">
-        <v>27</v>
+        <v>31</v>
       </c>
       <c r="E3">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="F3">
-        <v>77.14</v>
+        <v>88.56999999999999</v>
       </c>
       <c r="G3">
-        <v>22.86</v>
+        <v>11.43</v>
       </c>
       <c r="H3">
-        <v>7.7</v>
+        <v>8</v>
       </c>
       <c r="I3">
         <v>0</v>
@@ -3683,7 +3683,7 @@
     </row>
     <row r="4" spans="1:10">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="B4" t="s">
         <v>57</v>
@@ -3692,19 +3692,19 @@
         <v>35</v>
       </c>
       <c r="D4">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="E4">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="F4">
-        <v>88.56999999999999</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G4">
-        <v>11.43</v>
+        <v>5.71</v>
       </c>
       <c r="H4">
-        <v>8.1</v>
+        <v>7.9</v>
       </c>
       <c r="I4">
         <v>0</v>
@@ -3715,7 +3715,7 @@
     </row>
     <row r="5" spans="1:10">
       <c r="A5" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
       <c r="B5" t="s">
         <v>58</v>
@@ -3724,19 +3724,19 @@
         <v>35</v>
       </c>
       <c r="D5">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E5">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="F5">
-        <v>91.43000000000001</v>
+        <v>94.29000000000001</v>
       </c>
       <c r="G5">
-        <v>8.57</v>
+        <v>5.71</v>
       </c>
       <c r="H5">
-        <v>8.199999999999999</v>
+        <v>7.6</v>
       </c>
       <c r="I5">
         <v>0</v>
@@ -3747,7 +3747,7 @@
     </row>
     <row r="6" spans="1:10">
       <c r="A6" t="s">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="B6" t="s">
         <v>59</v>
@@ -3756,30 +3756,30 @@
         <v>35</v>
       </c>
       <c r="D6">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="E6">
         <v>0</v>
       </c>
       <c r="F6">
-        <v>91.43000000000001</v>
+        <v>100</v>
       </c>
       <c r="G6">
         <v>0</v>
       </c>
       <c r="H6">
-        <v>9.800000000000001</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="I6">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="J6">
-        <v>8.57</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
       <c r="A7" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="B7" t="s">
         <v>60</v>
@@ -3788,19 +3788,19 @@
         <v>35</v>
       </c>
       <c r="D7">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="E7">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F7">
-        <v>94.29000000000001</v>
+        <v>100</v>
       </c>
       <c r="G7">
-        <v>5.71</v>
+        <v>0</v>
       </c>
       <c r="H7">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="I7">
         <v>0</v>
@@ -3816,7 +3816,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F13"/>
+  <dimension ref="A1:F1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -3841,246 +3841,6 @@
       </c>
       <c r="F1" s="1" t="s">
         <v>11</v>
-      </c>
-    </row>
-    <row r="2" spans="1:6">
-      <c r="A2">
-        <v>20330051920122</v>
-      </c>
-      <c r="B2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" t="s">
-        <v>83</v>
-      </c>
-      <c r="E2" t="s">
-        <v>10</v>
-      </c>
-      <c r="F2" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6">
-      <c r="A3">
-        <v>20330051920122</v>
-      </c>
-      <c r="B3" t="s">
-        <v>65</v>
-      </c>
-      <c r="C3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D3" t="s">
-        <v>83</v>
-      </c>
-      <c r="E3" t="s">
-        <v>6</v>
-      </c>
-      <c r="F3" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="4" spans="1:6">
-      <c r="A4">
-        <v>20330051920126</v>
-      </c>
-      <c r="B4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C4" t="s">
-        <v>75</v>
-      </c>
-      <c r="D4" t="s">
-        <v>84</v>
-      </c>
-      <c r="E4" t="s">
-        <v>10</v>
-      </c>
-      <c r="F4" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="5" spans="1:6">
-      <c r="A5">
-        <v>20330051920135</v>
-      </c>
-      <c r="B5" t="s">
-        <v>67</v>
-      </c>
-      <c r="C5" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" t="s">
-        <v>84</v>
-      </c>
-      <c r="E5" t="s">
-        <v>10</v>
-      </c>
-      <c r="F5" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6">
-      <c r="A6">
-        <v>20330051920136</v>
-      </c>
-      <c r="B6" t="s">
-        <v>68</v>
-      </c>
-      <c r="C6" t="s">
-        <v>77</v>
-      </c>
-      <c r="D6" t="s">
-        <v>85</v>
-      </c>
-      <c r="E6" t="s">
-        <v>10</v>
-      </c>
-      <c r="F6" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6">
-      <c r="A7">
-        <v>20330051920136</v>
-      </c>
-      <c r="B7" t="s">
-        <v>68</v>
-      </c>
-      <c r="C7" t="s">
-        <v>77</v>
-      </c>
-      <c r="D7" t="s">
-        <v>85</v>
-      </c>
-      <c r="E7" t="s">
-        <v>6</v>
-      </c>
-      <c r="F7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6">
-      <c r="A8">
-        <v>20330051920141</v>
-      </c>
-      <c r="B8" t="s">
-        <v>69</v>
-      </c>
-      <c r="C8" t="s">
-        <v>78</v>
-      </c>
-      <c r="D8" t="s">
-        <v>86</v>
-      </c>
-      <c r="E8" t="s">
-        <v>10</v>
-      </c>
-      <c r="F8" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6">
-      <c r="A9">
-        <v>20330051920144</v>
-      </c>
-      <c r="B9" t="s">
-        <v>70</v>
-      </c>
-      <c r="C9" t="s">
-        <v>79</v>
-      </c>
-      <c r="D9" t="s">
-        <v>87</v>
-      </c>
-      <c r="E9" t="s">
-        <v>10</v>
-      </c>
-      <c r="F9" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6">
-      <c r="A10">
-        <v>20330051920144</v>
-      </c>
-      <c r="B10" t="s">
-        <v>70</v>
-      </c>
-      <c r="C10" t="s">
-        <v>79</v>
-      </c>
-      <c r="D10" t="s">
-        <v>87</v>
-      </c>
-      <c r="E10" t="s">
-        <v>6</v>
-      </c>
-      <c r="F10" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6">
-      <c r="A11">
-        <v>20330051920387</v>
-      </c>
-      <c r="B11" t="s">
-        <v>71</v>
-      </c>
-      <c r="C11" t="s">
-        <v>80</v>
-      </c>
-      <c r="D11" t="s">
-        <v>88</v>
-      </c>
-      <c r="E11" t="s">
-        <v>10</v>
-      </c>
-      <c r="F11" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6">
-      <c r="A12">
-        <v>20330051920148</v>
-      </c>
-      <c r="B12" t="s">
-        <v>72</v>
-      </c>
-      <c r="C12" t="s">
-        <v>81</v>
-      </c>
-      <c r="D12" t="s">
-        <v>89</v>
-      </c>
-      <c r="E12" t="s">
-        <v>10</v>
-      </c>
-      <c r="F12" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6">
-      <c r="A13">
-        <v>20330051920151</v>
-      </c>
-      <c r="B13" t="s">
-        <v>73</v>
-      </c>
-      <c r="C13" t="s">
-        <v>82</v>
-      </c>
-      <c r="D13" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" t="s">
-        <v>10</v>
-      </c>
-      <c r="F13" t="s">
-        <v>55</v>
       </c>
     </row>
   </sheetData>
@@ -4116,169 +3876,169 @@
     </row>
     <row r="2" spans="1:5">
       <c r="A2">
-        <v>20330051920122</v>
+        <v>20330051920115</v>
       </c>
       <c r="B2" t="s">
         <v>65</v>
       </c>
       <c r="C2" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="D2" t="s">
-        <v>83</v>
+        <v>118</v>
       </c>
       <c r="E2">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:5">
       <c r="A3">
-        <v>20330051920136</v>
+        <v>20330051920116</v>
       </c>
       <c r="B3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3" t="s">
-        <v>77</v>
+        <v>96</v>
       </c>
       <c r="D3" t="s">
-        <v>85</v>
+        <v>119</v>
       </c>
       <c r="E3">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:5">
       <c r="A4">
-        <v>20330051920144</v>
+        <v>20330051920118</v>
       </c>
       <c r="B4" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="C4" t="s">
-        <v>79</v>
+        <v>72</v>
       </c>
       <c r="D4" t="s">
-        <v>87</v>
+        <v>120</v>
       </c>
       <c r="E4">
-        <v>2</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:5">
       <c r="A5">
-        <v>20330051920126</v>
+        <v>20330051920119</v>
       </c>
       <c r="B5" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C5" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D5" t="s">
-        <v>84</v>
+        <v>121</v>
       </c>
       <c r="E5">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:5">
       <c r="A6">
-        <v>20330051920135</v>
+        <v>20330051920121</v>
       </c>
       <c r="B6" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C6" t="s">
-        <v>76</v>
+        <v>97</v>
       </c>
       <c r="D6" t="s">
-        <v>84</v>
+        <v>122</v>
       </c>
       <c r="E6">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:5">
       <c r="A7">
-        <v>20330051920141</v>
+        <v>20330051920122</v>
       </c>
       <c r="B7" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C7" t="s">
-        <v>78</v>
+        <v>98</v>
       </c>
       <c r="D7" t="s">
-        <v>86</v>
+        <v>123</v>
       </c>
       <c r="E7">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:5">
       <c r="A8">
-        <v>20330051920387</v>
+        <v>20330051920123</v>
       </c>
       <c r="B8" t="s">
         <v>71</v>
       </c>
       <c r="C8" t="s">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D8" t="s">
-        <v>88</v>
+        <v>124</v>
       </c>
       <c r="E8">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:5">
       <c r="A9">
-        <v>20330051920148</v>
+        <v>20330051920124</v>
       </c>
       <c r="B9" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C9" t="s">
-        <v>81</v>
+        <v>100</v>
       </c>
       <c r="D9" t="s">
-        <v>89</v>
+        <v>125</v>
       </c>
       <c r="E9">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:5">
       <c r="A10">
-        <v>20330051920151</v>
+        <v>20330051920125</v>
       </c>
       <c r="B10" t="s">
+        <v>72</v>
+      </c>
+      <c r="C10" t="s">
         <v>73</v>
       </c>
-      <c r="C10" t="s">
-        <v>82</v>
-      </c>
       <c r="D10" t="s">
-        <v>90</v>
+        <v>126</v>
       </c>
       <c r="E10">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:5">
       <c r="A11">
-        <v>20330051920115</v>
+        <v>20330051920126</v>
       </c>
       <c r="B11" t="s">
-        <v>91</v>
+        <v>73</v>
       </c>
       <c r="C11" t="s">
-        <v>65</v>
+        <v>72</v>
       </c>
       <c r="D11" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="E11">
         <v>0</v>
@@ -4286,16 +4046,16 @@
     </row>
     <row r="12" spans="1:5">
       <c r="A12">
-        <v>20330051920116</v>
+        <v>20330051920127</v>
       </c>
       <c r="B12" t="s">
-        <v>92</v>
+        <v>73</v>
       </c>
       <c r="C12" t="s">
-        <v>111</v>
+        <v>73</v>
       </c>
       <c r="D12" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="E12">
         <v>0</v>
@@ -4303,16 +4063,16 @@
     </row>
     <row r="13" spans="1:5">
       <c r="A13">
-        <v>20330051920118</v>
+        <v>20330051920128</v>
       </c>
       <c r="B13" t="s">
-        <v>93</v>
+        <v>73</v>
       </c>
       <c r="C13" t="s">
-        <v>75</v>
+        <v>101</v>
       </c>
       <c r="D13" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="E13">
         <v>0</v>
@@ -4320,16 +4080,16 @@
     </row>
     <row r="14" spans="1:5">
       <c r="A14">
-        <v>20330051920119</v>
+        <v>20330051920129</v>
       </c>
       <c r="B14" t="s">
-        <v>94</v>
+        <v>74</v>
       </c>
       <c r="C14" t="s">
-        <v>66</v>
+        <v>102</v>
       </c>
       <c r="D14" t="s">
-        <v>88</v>
+        <v>130</v>
       </c>
       <c r="E14">
         <v>0</v>
@@ -4337,16 +4097,16 @@
     </row>
     <row r="15" spans="1:5">
       <c r="A15">
-        <v>20330051920121</v>
+        <v>20330051920131</v>
       </c>
       <c r="B15" t="s">
-        <v>95</v>
+        <v>75</v>
       </c>
       <c r="C15" t="s">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="D15" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="E15">
         <v>0</v>
@@ -4354,16 +4114,16 @@
     </row>
     <row r="16" spans="1:5">
       <c r="A16">
-        <v>20330051920123</v>
+        <v>20330051920132</v>
       </c>
       <c r="B16" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C16" t="s">
-        <v>113</v>
+        <v>104</v>
       </c>
       <c r="D16" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="E16">
         <v>0</v>
@@ -4371,16 +4131,16 @@
     </row>
     <row r="17" spans="1:5">
       <c r="A17">
-        <v>20330051920124</v>
+        <v>20330051920133</v>
       </c>
       <c r="B17" t="s">
-        <v>96</v>
+        <v>76</v>
       </c>
       <c r="C17" t="s">
-        <v>114</v>
+        <v>105</v>
       </c>
       <c r="D17" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="E17">
         <v>0</v>
@@ -4388,16 +4148,16 @@
     </row>
     <row r="18" spans="1:5">
       <c r="A18">
-        <v>20330051920125</v>
+        <v>20330051920134</v>
       </c>
       <c r="B18" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C18" t="s">
-        <v>66</v>
+        <v>106</v>
       </c>
       <c r="D18" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="E18">
         <v>0</v>
@@ -4405,16 +4165,16 @@
     </row>
     <row r="19" spans="1:5">
       <c r="A19">
-        <v>20330051920127</v>
+        <v>20330051920135</v>
       </c>
       <c r="B19" t="s">
-        <v>66</v>
+        <v>78</v>
       </c>
       <c r="C19" t="s">
-        <v>66</v>
+        <v>107</v>
       </c>
       <c r="D19" t="s">
-        <v>133</v>
+        <v>127</v>
       </c>
       <c r="E19">
         <v>0</v>
@@ -4422,16 +4182,16 @@
     </row>
     <row r="20" spans="1:5">
       <c r="A20">
-        <v>20330051920128</v>
+        <v>20330051920136</v>
       </c>
       <c r="B20" t="s">
-        <v>66</v>
+        <v>79</v>
       </c>
       <c r="C20" t="s">
-        <v>115</v>
+        <v>81</v>
       </c>
       <c r="D20" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="E20">
         <v>0</v>
@@ -4439,16 +4199,16 @@
     </row>
     <row r="21" spans="1:5">
       <c r="A21">
-        <v>20330051920129</v>
+        <v>20330051920137</v>
       </c>
       <c r="B21" t="s">
-        <v>97</v>
+        <v>80</v>
       </c>
       <c r="C21" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="D21" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="E21">
         <v>0</v>
@@ -4456,16 +4216,16 @@
     </row>
     <row r="22" spans="1:5">
       <c r="A22">
-        <v>20330051920131</v>
+        <v>20330051920139</v>
       </c>
       <c r="B22" t="s">
-        <v>98</v>
+        <v>81</v>
       </c>
       <c r="C22" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="D22" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E22">
         <v>0</v>
@@ -4473,16 +4233,16 @@
     </row>
     <row r="23" spans="1:5">
       <c r="A23">
-        <v>20330051920132</v>
+        <v>19330051920387</v>
       </c>
       <c r="B23" t="s">
-        <v>99</v>
+        <v>82</v>
       </c>
       <c r="C23" t="s">
-        <v>118</v>
+        <v>71</v>
       </c>
       <c r="D23" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="E23">
         <v>0</v>
@@ -4490,16 +4250,16 @@
     </row>
     <row r="24" spans="1:5">
       <c r="A24">
-        <v>20330051920133</v>
+        <v>20330051920140</v>
       </c>
       <c r="B24" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="C24" t="s">
-        <v>119</v>
+        <v>107</v>
       </c>
       <c r="D24" t="s">
-        <v>138</v>
+        <v>121</v>
       </c>
       <c r="E24">
         <v>0</v>
@@ -4507,13 +4267,13 @@
     </row>
     <row r="25" spans="1:5">
       <c r="A25">
-        <v>20330051920134</v>
+        <v>20330051920141</v>
       </c>
       <c r="B25" t="s">
-        <v>100</v>
+        <v>84</v>
       </c>
       <c r="C25" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="D25" t="s">
         <v>139</v>
@@ -4524,13 +4284,13 @@
     </row>
     <row r="26" spans="1:5">
       <c r="A26">
-        <v>20330051920137</v>
+        <v>20330051920389</v>
       </c>
       <c r="B26" t="s">
-        <v>101</v>
+        <v>85</v>
       </c>
       <c r="C26" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="D26" t="s">
         <v>140</v>
@@ -4541,13 +4301,13 @@
     </row>
     <row r="27" spans="1:5">
       <c r="A27">
-        <v>20330051920139</v>
+        <v>20330051920142</v>
       </c>
       <c r="B27" t="s">
-        <v>77</v>
+        <v>86</v>
       </c>
       <c r="C27" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="D27" t="s">
         <v>141</v>
@@ -4558,13 +4318,13 @@
     </row>
     <row r="28" spans="1:5">
       <c r="A28">
-        <v>19330051920387</v>
+        <v>20330051920143</v>
       </c>
       <c r="B28" t="s">
-        <v>102</v>
+        <v>87</v>
       </c>
       <c r="C28" t="s">
-        <v>96</v>
+        <v>112</v>
       </c>
       <c r="D28" t="s">
         <v>142</v>
@@ -4575,16 +4335,16 @@
     </row>
     <row r="29" spans="1:5">
       <c r="A29">
-        <v>20330051920140</v>
+        <v>20330051920144</v>
       </c>
       <c r="B29" t="s">
-        <v>103</v>
+        <v>88</v>
       </c>
       <c r="C29" t="s">
-        <v>76</v>
+        <v>113</v>
       </c>
       <c r="D29" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="E29">
         <v>0</v>
@@ -4592,16 +4352,16 @@
     </row>
     <row r="30" spans="1:5">
       <c r="A30">
-        <v>20330051920389</v>
+        <v>20330051920387</v>
       </c>
       <c r="B30" t="s">
-        <v>104</v>
+        <v>89</v>
       </c>
       <c r="C30" t="s">
-        <v>123</v>
+        <v>114</v>
       </c>
       <c r="D30" t="s">
-        <v>143</v>
+        <v>121</v>
       </c>
       <c r="E30">
         <v>0</v>
@@ -4609,13 +4369,13 @@
     </row>
     <row r="31" spans="1:5">
       <c r="A31">
-        <v>20330051920142</v>
+        <v>20330051920145</v>
       </c>
       <c r="B31" t="s">
-        <v>105</v>
+        <v>90</v>
       </c>
       <c r="C31" t="s">
-        <v>119</v>
+        <v>76</v>
       </c>
       <c r="D31" t="s">
         <v>144</v>
@@ -4626,13 +4386,13 @@
     </row>
     <row r="32" spans="1:5">
       <c r="A32">
-        <v>20330051920143</v>
+        <v>20330051920148</v>
       </c>
       <c r="B32" t="s">
-        <v>106</v>
+        <v>91</v>
       </c>
       <c r="C32" t="s">
-        <v>124</v>
+        <v>115</v>
       </c>
       <c r="D32" t="s">
         <v>145</v>
@@ -4643,13 +4403,13 @@
     </row>
     <row r="33" spans="1:5">
       <c r="A33">
-        <v>20330051920145</v>
+        <v>20330051920150</v>
       </c>
       <c r="B33" t="s">
-        <v>107</v>
+        <v>92</v>
       </c>
       <c r="C33" t="s">
-        <v>99</v>
+        <v>116</v>
       </c>
       <c r="D33" t="s">
         <v>146</v>
@@ -4660,13 +4420,13 @@
     </row>
     <row r="34" spans="1:5">
       <c r="A34">
-        <v>20330051920150</v>
+        <v>20330051920151</v>
       </c>
       <c r="B34" t="s">
-        <v>108</v>
+        <v>93</v>
       </c>
       <c r="C34" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="D34" t="s">
         <v>147</v>
@@ -4680,7 +4440,7 @@
         <v>20330051920153</v>
       </c>
       <c r="B35" t="s">
-        <v>109</v>
+        <v>94</v>
       </c>
       <c r="D35" t="s">
         <v>148</v>
@@ -4694,10 +4454,10 @@
         <v>20330051920154</v>
       </c>
       <c r="B36" t="s">
-        <v>110</v>
+        <v>95</v>
       </c>
       <c r="C36" t="s">
-        <v>92</v>
+        <v>66</v>
       </c>
       <c r="D36" t="s">
         <v>149</v>
@@ -4713,7 +4473,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="30.7109375" customWidth="1"/>
@@ -4745,22 +4505,22 @@
     </row>
     <row r="2" spans="1:7">
       <c r="A2">
-        <v>20330051920387</v>
+        <v>20330051920126</v>
       </c>
       <c r="B2" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C2" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D2" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="E2" t="s">
         <v>9</v>
       </c>
       <c r="F2" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4768,16 +4528,16 @@
     </row>
     <row r="3" spans="1:7">
       <c r="A3">
-        <v>20330051920387</v>
+        <v>20330051920126</v>
       </c>
       <c r="B3" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C3" t="s">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="D3" t="s">
-        <v>88</v>
+        <v>127</v>
       </c>
       <c r="E3" t="s">
         <v>10</v>
@@ -4786,27 +4546,27 @@
         <v>55</v>
       </c>
       <c r="G3">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="4" spans="1:7">
       <c r="A4">
-        <v>20330051920151</v>
+        <v>20330051920119</v>
       </c>
       <c r="B4" t="s">
+        <v>68</v>
+      </c>
+      <c r="C4" t="s">
         <v>73</v>
       </c>
-      <c r="C4" t="s">
-        <v>82</v>
-      </c>
       <c r="D4" t="s">
-        <v>90</v>
+        <v>121</v>
       </c>
       <c r="E4" t="s">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="F4" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="G4">
         <v>5</v>
@@ -4814,16 +4574,16 @@
     </row>
     <row r="5" spans="1:7">
       <c r="A5">
-        <v>20330051920151</v>
+        <v>20330051920122</v>
       </c>
       <c r="B5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="C5" t="s">
-        <v>82</v>
+        <v>98</v>
       </c>
       <c r="D5" t="s">
-        <v>90</v>
+        <v>123</v>
       </c>
       <c r="E5" t="s">
         <v>10</v>
@@ -4832,29 +4592,75 @@
         <v>55</v>
       </c>
       <c r="G5">
-        <v>-1</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:7">
       <c r="A6">
-        <v>20330051920119</v>
+        <v>20330051920136</v>
       </c>
       <c r="B6" t="s">
-        <v>94</v>
+        <v>79</v>
       </c>
       <c r="C6" t="s">
-        <v>66</v>
+        <v>81</v>
       </c>
       <c r="D6" t="s">
-        <v>88</v>
+        <v>135</v>
       </c>
       <c r="E6" t="s">
-        <v>7</v>
+        <v>5</v>
       </c>
       <c r="F6" t="s">
-        <v>60</v>
+        <v>56</v>
       </c>
       <c r="G6">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7">
+      <c r="A7">
+        <v>20330051920387</v>
+      </c>
+      <c r="B7" t="s">
+        <v>89</v>
+      </c>
+      <c r="C7" t="s">
+        <v>114</v>
+      </c>
+      <c r="D7" t="s">
+        <v>121</v>
+      </c>
+      <c r="E7" t="s">
+        <v>10</v>
+      </c>
+      <c r="F7" t="s">
+        <v>55</v>
+      </c>
+      <c r="G7">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7">
+      <c r="A8">
+        <v>20330051920148</v>
+      </c>
+      <c r="B8" t="s">
+        <v>91</v>
+      </c>
+      <c r="C8" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" t="s">
+        <v>5</v>
+      </c>
+      <c r="F8" t="s">
+        <v>56</v>
+      </c>
+      <c r="G8">
         <v>5</v>
       </c>
     </row>
